--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 00:25:49</t>
+          <t>2026-06-28 02:38:07</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 00:25:49</t>
+          <t>2026-06-28 02:38:07</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G4" t="n">
         <v>1.74</v>
@@ -1398,7 +1398,7 @@
         <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 00:25:49</t>
+          <t>2026-06-28 02:38:07</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 00:25:49</t>
+          <t>2026-06-28 02:38:07</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 00:25:49</t>
+          <t>2026-06-28 02:38:07</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
         <v>2.32</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 00:25:49</t>
+          <t>2026-06-28 02:38:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 02:38:07</t>
+          <t>2026-06-28 04:50:33</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 02:38:07</t>
+          <t>2026-06-28 04:50:33</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>6.4</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>3.55</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 02:38:07</t>
+          <t>2026-06-28 04:50:33</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 02:38:07</t>
+          <t>2026-06-28 04:50:33</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 02:38:07</t>
+          <t>2026-06-28 04:50:33</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 02:38:07</t>
+          <t>2026-06-28 04:50:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 04:50:33</t>
+          <t>2026-06-28 07:03:39</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 04:50:33</t>
+          <t>2026-06-28 07:03:39</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G4" t="n">
         <v>1.74</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 04:50:33</t>
+          <t>2026-06-28 07:03:39</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 04:50:33</t>
+          <t>2026-06-28 07:03:39</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 04:50:33</t>
+          <t>2026-06-28 07:03:39</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 04:50:33</t>
+          <t>2026-06-28 07:03:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 07:03:39</t>
+          <t>2026-06-28 09:15:53</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 07:03:39</t>
+          <t>2026-06-28 09:15:53</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G4" t="n">
         <v>1.74</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 07:03:39</t>
+          <t>2026-06-28 09:15:53</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 07:03:39</t>
+          <t>2026-06-28 09:15:53</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 07:03:39</t>
+          <t>2026-06-28 09:15:53</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 07:03:39</t>
+          <t>2026-06-28 09:15:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 09:15:53</t>
+          <t>2026-06-28 11:26:33</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 09:15:53</t>
+          <t>2026-06-28 11:26:33</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G4" t="n">
         <v>1.74</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 09:15:53</t>
+          <t>2026-06-28 11:26:33</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 09:15:53</t>
+          <t>2026-06-28 11:26:33</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 09:15:53</t>
+          <t>2026-06-28 11:26:33</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 09:15:53</t>
+          <t>2026-06-28 11:26:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -869,208 +869,208 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 11:26:33</t>
+          <t>2026-06-28 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1129,202 +1129,202 @@
         <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 11:26:33</t>
+          <t>2026-06-28 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G4" t="n">
         <v>1.74</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 11:26:33</t>
+          <t>2026-06-28 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 11:26:33</t>
+          <t>2026-06-28 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 11:26:33</t>
+          <t>2026-06-28 13:36:45</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="G7" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 11:26:33</t>
+          <t>2026-06-28 13:36:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O2" t="n">
         <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
         <v>1.16</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 13:36:45</t>
+          <t>2026-06-28 15:45:53</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
         <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q3" t="n">
         <v>1.14</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 13:36:45</t>
+          <t>2026-06-28 15:45:53</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G4" t="n">
         <v>1.74</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 13:36:45</t>
+          <t>2026-06-28 15:45:53</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 13:36:45</t>
+          <t>2026-06-28 15:45:53</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 13:36:45</t>
+          <t>2026-06-28 15:45:53</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 13:36:45</t>
+          <t>2026-06-28 15:45:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1.16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
         <v>1.14</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G4" t="n">
         <v>1.74</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -881,19 +881,19 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O2" t="n">
         <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q2" t="n">
         <v>1.16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
         <v>1.16</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
         <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q3" t="n">
         <v>1.14</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G4" t="n">
         <v>1.74</v>
@@ -1383,202 +1383,202 @@
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>1.56</v>
       </c>
       <c r="H2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
@@ -1404,13 +1404,13 @@
         <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
         <v>1.12</v>
@@ -1479,10 +1479,10 @@
         <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>180</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
         <v>5</v>
@@ -1494,7 +1494,7 @@
         <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>95</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
         <v>6.4</v>
@@ -1506,7 +1506,7 @@
         <v>19.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>90</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
         <v>12</v>
@@ -1515,16 +1515,16 @@
         <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>140</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>160</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
@@ -1536,13 +1536,13 @@
         <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
         <v>4.1</v>
@@ -1554,31 +1554,31 @@
         <v>12</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>10.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>50</v>
+        <v>9.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>55</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
@@ -1891,16 +1891,16 @@
         <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
         <v>1.68</v>
@@ -1909,184 +1909,184 @@
         <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
@@ -2145,16 +2145,16 @@
         <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P7" t="n">
         <v>1.5</v>
@@ -2163,184 +2163,184 @@
         <v>2.58</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -863,13 +863,13 @@
         <v>1.56</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>2.86</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1368,22 @@
         <v>1.61</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="H4" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="I4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1395,7 +1395,7 @@
         <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
         <v>2.22</v>
@@ -1410,25 +1410,25 @@
         <v>2.16</v>
       </c>
       <c r="U4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
         <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA4" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AB4" t="n">
         <v>8</v>
@@ -1440,7 +1440,7 @@
         <v>34</v>
       </c>
       <c r="AE4" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF4" t="n">
         <v>10.5</v>
@@ -1449,7 +1449,7 @@
         <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
         <v>160</v>
@@ -1470,115 +1470,115 @@
         <v>16.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.4</v>
+        <v>3.35</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.5</v>
+        <v>3.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="AV4" t="n">
-        <v>20</v>
+        <v>3.95</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>3.15</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.6</v>
+        <v>3.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.5</v>
+        <v>3.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>12</v>
+        <v>3.65</v>
       </c>
       <c r="BC4" t="n">
-        <v>15</v>
+        <v>3.75</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>9.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4" t="n">
         <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
         <v>10.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
         <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>1.87</v>
@@ -1769,7 +1769,7 @@
         <v>7</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5" t="n">
         <v>8.6</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>
@@ -1879,28 +1879,28 @@
         <v>2.16</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
         <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.48</v>
+        <v>2.98</v>
       </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
         <v>1.68</v>
@@ -1909,130 +1909,130 @@
         <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
         <v>1.86</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH6" t="n">
         <v>3.45</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
@@ -2241,16 +2241,16 @@
         <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS7" t="n">
         <v>5.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
         <v>17.5</v>
@@ -2277,7 +2277,7 @@
         <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE7" t="n">
         <v>5.1</v>
@@ -2298,13 +2298,13 @@
         <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
         <v>4.6</v>
@@ -2313,34 +2313,34 @@
         <v>3.55</v>
       </c>
       <c r="BP7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ7" t="n">
         <v>6.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT7" t="n">
         <v>8.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>9.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="G4" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1395,7 +1395,7 @@
         <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q4" t="n">
         <v>2.22</v>
@@ -1416,7 +1416,7 @@
         <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
@@ -1428,10 +1428,10 @@
         <v>70</v>
       </c>
       <c r="AA4" t="n">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="AB4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
@@ -1455,7 +1455,7 @@
         <v>160</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AK4" t="n">
         <v>25</v>
@@ -1467,118 +1467,118 @@
         <v>250</v>
       </c>
       <c r="AN4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO4" t="n">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="AP4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY4" t="n">
         <v>3.35</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="AZ4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA4" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.3</v>
       </c>
       <c r="BB4" t="n">
         <v>3.65</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="BP4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>
@@ -1625,46 +1625,46 @@
         <v>2.46</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
         <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O5" t="n">
         <v>1.47</v>
       </c>
       <c r="P5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S5" t="n">
         <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V5" t="n">
         <v>1.32</v>
@@ -1673,13 +1673,13 @@
         <v>1.68</v>
       </c>
       <c r="X5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y5" t="n">
         <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="n">
         <v>100</v>
@@ -1691,7 +1691,7 @@
         <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE5" t="n">
         <v>70</v>
@@ -1700,10 +1700,10 @@
         <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
         <v>90</v>
@@ -1712,7 +1712,7 @@
         <v>42</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
         <v>65</v>
@@ -1727,7 +1727,7 @@
         <v>85</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>9.800000000000001</v>
@@ -1736,7 +1736,7 @@
         <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT5" t="n">
         <v>6.6</v>
@@ -1760,34 +1760,34 @@
         <v>17</v>
       </c>
       <c r="BA5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB5" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB5" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BC5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
         <v>23</v>
       </c>
       <c r="BG5" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK5" t="n">
         <v>7.4</v>
@@ -1808,10 +1808,10 @@
         <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
         <v>8.6</v>
@@ -1823,16 +1823,16 @@
         <v>5.7</v>
       </c>
       <c r="BV5" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX5" t="n">
         <v>70</v>
       </c>
       <c r="BY5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -1885,19 +1885,19 @@
         <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O6" t="n">
         <v>1.4</v>
@@ -1906,7 +1906,7 @@
         <v>1.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
@@ -1915,28 +1915,28 @@
         <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V6" t="n">
         <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X6" t="n">
         <v>13</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB6" t="n">
         <v>9</v>
@@ -1948,7 +1948,7 @@
         <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
@@ -1978,115 +1978,115 @@
         <v>23</v>
       </c>
       <c r="AO6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AQ6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX6" t="n">
         <v>3.9</v>
       </c>
-      <c r="AR6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW6" t="n">
+      <c r="AY6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD6" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BE6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF6" t="n">
         <v>4.3</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BG6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN6" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO6" t="n">
-        <v>1.42</v>
+        <v>3.75</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.42</v>
+        <v>6.2</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.42</v>
+        <v>7.8</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.42</v>
+        <v>5.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.42</v>
+        <v>8</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.42</v>
+        <v>8.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I7" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
         <v>2.94</v>
@@ -2145,7 +2145,7 @@
         <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
@@ -2172,25 +2172,25 @@
         <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA7" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB7" t="n">
         <v>7.4</v>
@@ -2199,10 +2199,10 @@
         <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="n">
         <v>12.5</v>
@@ -2211,13 +2211,13 @@
         <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK7" t="n">
         <v>34</v>
@@ -2226,73 +2226,73 @@
         <v>70</v>
       </c>
       <c r="AM7" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN7" t="n">
         <v>30</v>
       </c>
       <c r="AO7" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.6</v>
+        <v>3.55</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD7" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BE7" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>19.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7" t="n">
         <v>12.5</v>
@@ -2304,43 +2304,43 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>2.22</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="BP7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.6</v>
+        <v>2.12</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU7" t="n">
         <v>4.6</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.800000000000001</v>
+        <v>2.14</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.199999999999999</v>
+        <v>2.16</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="G2" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="H2" t="n">
-        <v>2.86</v>
+        <v>10.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.32</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>1.32</v>
+        <v>2.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>1.16</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.09</v>
       </c>
-      <c r="G3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1177,100 +1177,100 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1294,7 +1294,7 @@
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>CA Claypole</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anapolis GO</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>1.68</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>1.08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.68</v>
+        <v>1.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,192 +1605,192 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>SER Caxias do Sul</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Anapolis GO</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>1.59</v>
       </c>
       <c r="G5" t="n">
-        <v>2.46</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="I5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K5" t="n">
         <v>4.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.15</v>
       </c>
       <c r="L5" t="n">
         <v>1.45</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>2.42</v>
       </c>
       <c r="X5" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="AA5" t="n">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="AE5" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AJ5" t="n">
-        <v>42</v>
+        <v>18.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>170</v>
+        <v>240</v>
       </c>
       <c r="AN5" t="n">
-        <v>36</v>
+        <v>15.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>85</v>
+        <v>260</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.6</v>
+        <v>2.94</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>38</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>12</v>
+        <v>3.25</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.800000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>4.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="BC5" t="n">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,57 +1799,57 @@
         <v>10</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BT5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BV5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,244 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.47</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="P6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.84</v>
-      </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AA6" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AB6" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AD6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
         <v>21</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>24</v>
       </c>
       <c r="AI6" t="n">
         <v>90</v>
       </c>
       <c r="AJ6" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF6" t="n">
         <v>23</v>
       </c>
-      <c r="AO6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG6" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BJ6" t="n">
         <v>11</v>
       </c>
       <c r="BK6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN6" t="n">
         <v>5.2</v>
       </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
+      <c r="BO6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
         <v>9.4</v>
       </c>
-      <c r="BN6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BT6" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>
@@ -2118,229 +2118,229 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Amazonas FC</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="O7" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W7" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X7" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
         <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG7" t="n">
-        <v>13</v>
-      </c>
       <c r="AH7" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="n">
         <v>29</v>
       </c>
       <c r="AK7" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
         <v>3.35</v>
       </c>
       <c r="AV7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB7" t="n">
         <v>4.5</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BC7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK7" t="n">
         <v>5.3</v>
       </c>
-      <c r="AX7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.12</v>
+        <v>8</v>
       </c>
       <c r="BT7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BU7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>2.14</v>
-      </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,261 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Amazonas FC</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,28 +857,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="G2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="H2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.22</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
         <v>5.3</v>
@@ -893,28 +893,28 @@
         <v>1.49</v>
       </c>
       <c r="R2" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="X2" t="n">
         <v>36</v>
       </c>
       <c r="Y2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Z2" t="n">
         <v>170</v>
@@ -926,13 +926,13 @@
         <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD2" t="n">
         <v>55</v>
       </c>
       <c r="AE2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
@@ -941,10 +941,10 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AJ2" t="n">
         <v>10</v>
@@ -959,64 +959,64 @@
         <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>3.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="n">
         <v>4.9</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
@@ -1120,10 +1120,10 @@
         <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K3" t="n">
         <v>7.8</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
@@ -1150,7 +1150,7 @@
         <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="T3" t="n">
         <v>1.79</v>
@@ -1159,7 +1159,7 @@
         <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
         <v>3.2</v>
@@ -1219,25 +1219,25 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS3" t="n">
         <v>4.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
         <v>3.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
@@ -1246,25 +1246,25 @@
         <v>3.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB3" t="n">
         <v>3.95</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
         <v>3.85</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
@@ -1351,126 +1351,126 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CA Claypole</t>
+          <t>CSD Central Ballester</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Canuelas</t>
+          <t>CA Atlas</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>3.15</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.08</v>
+        <v>2.14</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="P4" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
         <v>1.03</v>
@@ -1521,81 +1521,81 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>CA Claypole</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anapolis GO</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.59</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7</v>
+        <v>110</v>
       </c>
       <c r="H5" t="n">
-        <v>5.9</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
-        <v>9.199999999999999</v>
+        <v>110</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.08</v>
       </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.26</v>
-      </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>1.58</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.94</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>SER Caxias do Sul</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Anapolis GO</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>1.59</v>
       </c>
       <c r="G6" t="n">
-        <v>2.46</v>
+        <v>1.71</v>
       </c>
       <c r="H6" t="n">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="I6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S6" t="n">
         <v>4.1</v>
       </c>
-      <c r="J6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="T6" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="X6" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>260</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BQ6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
         <v>8</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BT6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BE6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>9</v>
-      </c>
       <c r="BX6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,244 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.15</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.75</v>
       </c>
       <c r="L7" t="n">
         <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="P7" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AB7" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AD7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH7" t="n">
         <v>21</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AK7" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AO7" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.95</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.7</v>
+        <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
         <v>6.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.9</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.4</v>
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BJ7" t="n">
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
@@ -2372,229 +2372,229 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Amazonas FC</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.18</v>
       </c>
-      <c r="H8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.58</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="X8" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
         <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG8" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG8" t="n">
-        <v>13</v>
-      </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
         <v>29</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AR8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD8" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BE8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK8" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU8" t="n">
         <v>4.5</v>
       </c>
-      <c r="AW8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BV8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,261 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Amazonas FC</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -863,46 +863,46 @@
         <v>1.3</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="I2" t="n">
         <v>16</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K2" t="n">
         <v>7.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
@@ -911,112 +911,112 @@
         <v>4.3</v>
       </c>
       <c r="X2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL2" t="n">
         <v>55</v>
       </c>
-      <c r="AE2" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>40</v>
-      </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AO2" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>1.84</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.5</v>
+        <v>2.18</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>1.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.9</v>
+        <v>1.84</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.7</v>
+        <v>1.93</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.2</v>
+        <v>1.67</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.2</v>
+        <v>1.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.4</v>
+        <v>2.08</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.25</v>
+        <v>1.88</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="BH2" t="n">
         <v>4.9</v>
@@ -1034,13 +1034,13 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>3.95</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP2" t="n">
         <v>7</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -1135,28 +1135,28 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="Q3" t="n">
         <v>1.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="S3" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
         <v>1.79</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
         <v>1.1</v>
@@ -1219,10 +1219,10 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
         <v>4.2</v>
@@ -1231,13 +1231,13 @@
         <v>4.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AU3" t="n">
         <v>3.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
@@ -1249,7 +1249,7 @@
         <v>3.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BA3" t="n">
         <v>4.2</v>
@@ -1258,16 +1258,16 @@
         <v>3.95</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BE3" t="n">
         <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BG3" t="n">
         <v>4</v>
@@ -1294,7 +1294,7 @@
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="I4" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="J4" t="n">
         <v>2.64</v>
@@ -1386,16 +1386,16 @@
         <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N4" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="O4" t="n">
         <v>1.68</v>
       </c>
       <c r="P4" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="Q4" t="n">
         <v>2.9</v>
@@ -1404,7 +1404,7 @@
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="T4" t="n">
         <v>2.3</v>
@@ -1413,46 +1413,46 @@
         <v>1.58</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X4" t="n">
         <v>7.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA4" t="n">
         <v>50</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
         <v>110</v>
@@ -1473,58 +1473,58 @@
         <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF4" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BH4" t="n">
         <v>2.5</v>
@@ -1536,59 +1536,59 @@
         <v>13.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="BN4" t="n">
         <v>7.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.93</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.97</v>
       </c>
       <c r="BT4" t="n">
         <v>5.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>18.5</v>
+        <v>1.87</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -1619,175 +1619,175 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S5" t="n">
         <v>1.02</v>
       </c>
-      <c r="G5" t="n">
-        <v>110</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I5" t="n">
-        <v>110</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K5" t="n">
-        <v>950</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.58</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
@@ -1799,50 +1799,50 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS5" t="n">
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW5" t="n">
         <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY5" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="CA5" t="n">
         <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -1873,31 +1873,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G6" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H6" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="I6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>1.41</v>
@@ -1915,7 +1915,7 @@
         <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
         <v>1.72</v>
@@ -1924,10 +1924,10 @@
         <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
         <v>21</v>
@@ -1936,10 +1936,10 @@
         <v>70</v>
       </c>
       <c r="AA6" t="n">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC6" t="n">
         <v>11</v>
@@ -1966,7 +1966,7 @@
         <v>18.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
         <v>60</v>
@@ -1978,115 +1978,115 @@
         <v>15.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AR6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW6" t="n">
+      <c r="AX6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.6</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN6" t="n">
         <v>4.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP6" t="n">
         <v>12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT6" t="n">
         <v>11</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G7" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I7" t="n">
         <v>4.1</v>
@@ -2145,52 +2145,52 @@
         <v>3.15</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="O7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V7" t="n">
         <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X7" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA7" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="n">
         <v>8.199999999999999</v>
@@ -2199,13 +2199,13 @@
         <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -2214,7 +2214,7 @@
         <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
         <v>42</v>
@@ -2223,28 +2223,28 @@
         <v>36</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
         <v>6.6</v>
@@ -2253,10 +2253,10 @@
         <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW7" t="n">
-        <v>38</v>
+        <v>8.4</v>
       </c>
       <c r="AX7" t="n">
         <v>13</v>
@@ -2268,28 +2268,28 @@
         <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BI7" t="n">
         <v>2.58</v>
@@ -2304,10 +2304,10 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO7" t="n">
         <v>4.4</v>
@@ -2316,41 +2316,41 @@
         <v>21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BT7" t="n">
         <v>7</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV7" t="n">
         <v>36</v>
       </c>
       <c r="BW7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>9</v>
       </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>10</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
@@ -2405,7 +2405,7 @@
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>1.4</v>
@@ -2432,7 +2432,7 @@
         <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2471,10 +2471,10 @@
         <v>90</v>
       </c>
       <c r="AJ8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK8" t="n">
         <v>29</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>28</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
@@ -2483,22 +2483,22 @@
         <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
         <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
@@ -2507,40 +2507,40 @@
         <v>6.6</v>
       </c>
       <c r="AV8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>4.3</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BA8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD8" t="n">
         <v>5</v>
       </c>
-      <c r="AX8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA8" t="n">
+      <c r="BE8" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.2</v>
       </c>
       <c r="BF8" t="n">
         <v>4.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="n">
         <v>3.15</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>2.18</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
         <v>5.6</v>
@@ -2665,10 +2665,10 @@
         <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2677,16 +2677,16 @@
         <v>5.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
         <v>1.69</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X9" t="n">
         <v>9.800000000000001</v>
@@ -2695,7 +2695,7 @@
         <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA9" t="n">
         <v>170</v>
@@ -2713,7 +2713,7 @@
         <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
         <v>13</v>
@@ -2722,10 +2722,10 @@
         <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK9" t="n">
         <v>34</v>
@@ -2737,22 +2737,22 @@
         <v>250</v>
       </c>
       <c r="AN9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO9" t="n">
         <v>180</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AT9" t="n">
         <v>5.6</v>
@@ -2761,40 +2761,40 @@
         <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BD9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE9" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE9" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BF9" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH9" t="n">
         <v>2.8</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -869,10 +869,10 @@
         <v>16</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="K2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.25</v>
@@ -887,22 +887,22 @@
         <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="Q2" t="n">
         <v>1.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
@@ -911,112 +911,112 @@
         <v>4.3</v>
       </c>
       <c r="X2" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>34</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>46</v>
-      </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>330</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT2" t="n">
         <v>5.1</v>
       </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AU2" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.84</v>
+        <v>7.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.84</v>
+        <v>8.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.84</v>
+        <v>4.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.93</v>
+        <v>5.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.84</v>
+        <v>8.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.67</v>
+        <v>4.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.08</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.84</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.88</v>
+        <v>3.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.84</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="n">
         <v>4.9</v>
@@ -1040,7 +1040,7 @@
         <v>3.95</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP2" t="n">
         <v>7</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
@@ -1225,7 +1225,7 @@
         <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AS3" t="n">
         <v>4.1</v>
@@ -1252,19 +1252,19 @@
         <v>3.95</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
         <v>3.95</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
         <v>4.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
         <v>3.45</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="I4" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="K4" t="n">
         <v>3.15</v>
@@ -1386,73 +1386,73 @@
         <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="O4" t="n">
         <v>1.68</v>
       </c>
       <c r="P4" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
         <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V4" t="n">
         <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X4" t="n">
         <v>7.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA4" t="n">
         <v>50</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG4" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
         <v>110</v>
@@ -1473,58 +1473,58 @@
         <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AX4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG4" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>5.6</v>
       </c>
       <c r="BH4" t="n">
         <v>2.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G5" t="n">
         <v>3.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="K5" t="n">
         <v>3.2</v>
@@ -1643,13 +1643,13 @@
         <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="O5" t="n">
         <v>1.64</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q5" t="n">
         <v>2.92</v>
@@ -1658,13 +1658,13 @@
         <v>1.15</v>
       </c>
       <c r="S5" t="n">
-        <v>1.02</v>
+        <v>6.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
         <v>1.4</v>
@@ -1676,7 +1676,7 @@
         <v>7.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
         <v>22</v>
@@ -1685,7 +1685,7 @@
         <v>75</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC5" t="n">
         <v>8</v>
@@ -1706,7 +1706,7 @@
         <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
         <v>75</v>
@@ -1715,10 +1715,10 @@
         <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM5" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN5" t="n">
         <v>95</v>
@@ -1727,58 +1727,58 @@
         <v>95</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.15</v>
+        <v>5.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="AS5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA5" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW5" t="n">
+      <c r="BB5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB5" t="n">
+      <c r="BE5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF5" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BG5" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5</v>
       </c>
       <c r="BH5" t="n">
         <v>2.58</v>
@@ -1790,59 +1790,59 @@
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BN5" t="n">
         <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP5" t="n">
         <v>34</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR5" t="n">
         <v>70</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BT5" t="n">
         <v>6.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV5" t="n">
         <v>34</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX5" t="n">
         <v>70</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BZ5" t="n">
         <v>80</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="G6" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="I6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
         <v>4.1</v>
@@ -1894,7 +1894,7 @@
         <v>1.46</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
         <v>3.05</v>
@@ -1906,187 +1906,187 @@
         <v>1.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
         <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z6" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AA6" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="AB6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC6" t="n">
         <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AE6" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI6" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AJ6" t="n">
         <v>18.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AN6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.45</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.75</v>
+        <v>14.5</v>
       </c>
       <c r="AR6" t="n">
         <v>4.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AW6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.5</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
         <v>9.6</v>
       </c>
-      <c r="BN6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -2145,7 +2145,7 @@
         <v>3.15</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
@@ -2154,22 +2154,22 @@
         <v>2.88</v>
       </c>
       <c r="O7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P7" t="n">
         <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
         <v>1.92</v>
@@ -2289,10 +2289,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7" t="n">
         <v>11</v>
@@ -2304,53 +2304,53 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP7" t="n">
         <v>21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BR7" t="n">
         <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
@@ -2411,10 +2411,10 @@
         <v>1.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
         <v>1.25</v>
@@ -2432,19 +2432,19 @@
         <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA8" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB8" t="n">
         <v>9</v>
@@ -2480,7 +2480,7 @@
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN8" t="n">
         <v>24</v>
@@ -2489,16 +2489,16 @@
         <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.75</v>
+        <v>9.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
@@ -2507,40 +2507,40 @@
         <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG8" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5</v>
       </c>
       <c r="BH8" t="n">
         <v>3.15</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G9" t="n">
         <v>2.18</v>
@@ -2647,28 +2647,28 @@
         <v>5.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2677,31 +2677,31 @@
         <v>5.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y9" t="n">
         <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA9" t="n">
         <v>170</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC9" t="n">
         <v>8.4</v>
@@ -2734,7 +2734,7 @@
         <v>70</v>
       </c>
       <c r="AM9" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN9" t="n">
         <v>32</v>
@@ -2743,13 +2743,13 @@
         <v>180</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AS9" t="n">
         <v>5.1</v>
@@ -2767,13 +2767,13 @@
         <v>5</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BA9" t="n">
         <v>5</v>
@@ -2782,16 +2782,16 @@
         <v>20</v>
       </c>
       <c r="BC9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
         <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BG9" t="n">
         <v>5.1</v>
@@ -2806,7 +2806,7 @@
         <v>12.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,13 +2818,13 @@
         <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="BP9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR9" t="n">
         <v>44</v>
@@ -2833,22 +2833,22 @@
         <v>8.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
         <v>55</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -857,178 +857,178 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L2" t="n">
         <v>1.24</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.25</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="T2" t="n">
         <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="X2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>180</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH2" t="n">
         <v>50</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>34</v>
       </c>
       <c r="AI2" t="n">
         <v>190</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AK2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>190</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
         <v>330</v>
       </c>
       <c r="AP2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV2" t="n">
         <v>7</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AW2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH2" t="n">
         <v>5.1</v>
       </c>
-      <c r="AU2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BI2" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,40 +1037,40 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BP2" t="n">
         <v>7</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BR2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
@@ -1144,7 +1144,7 @@
         <v>2.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R3" t="n">
         <v>1.56</v>
@@ -1195,7 +1195,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1219,58 +1219,58 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AQ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR3" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4</v>
       </c>
       <c r="AS3" t="n">
         <v>4.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AV3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW3" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW3" t="n">
-        <v>4</v>
-      </c>
       <c r="AX3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB3" t="n">
         <v>3.8</v>
       </c>
-      <c r="AY3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ3" t="n">
+      <c r="BC3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD3" t="n">
         <v>3.95</v>
       </c>
-      <c r="BA3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
         <v>3.45</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1371,13 +1371,13 @@
         <v>4.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="I4" t="n">
         <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="K4" t="n">
         <v>3.15</v>
@@ -1398,13 +1398,13 @@
         <v>1.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="T4" t="n">
         <v>2.3</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>2.7</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J5" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="K5" t="n">
         <v>3.2</v>
@@ -1643,7 +1643,7 @@
         <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.64</v>
@@ -1676,16 +1676,16 @@
         <v>7.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
         <v>75</v>
       </c>
       <c r="AB5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5" t="n">
         <v>8</v>
@@ -1697,7 +1697,7 @@
         <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>18</v>
@@ -1727,58 +1727,58 @@
         <v>95</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AV5" t="n">
         <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF5" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF5" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH5" t="n">
         <v>2.58</v>
@@ -1790,7 +1790,7 @@
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G6" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -1918,7 +1918,7 @@
         <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V6" t="n">
         <v>1.12</v>
@@ -1930,19 +1930,19 @@
         <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z6" t="n">
         <v>85</v>
       </c>
       <c r="AA6" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="AB6" t="n">
         <v>7.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD6" t="n">
         <v>38</v>
@@ -1963,7 +1963,7 @@
         <v>190</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
         <v>25</v>
@@ -1978,19 +1978,19 @@
         <v>15</v>
       </c>
       <c r="AO6" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>14.5</v>
       </c>
       <c r="AR6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS6" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
         <v>5.5</v>
@@ -2008,10 +2008,10 @@
         <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
         <v>4.3</v>
@@ -2023,16 +2023,16 @@
         <v>17</v>
       </c>
       <c r="BD6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.4</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH6" t="n">
         <v>3.2</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
         <v>3.95</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>2.36</v>
       </c>
       <c r="G7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H7" t="n">
         <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -2184,7 +2184,7 @@
         <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
         <v>26</v>
@@ -2205,7 +2205,7 @@
         <v>60</v>
       </c>
       <c r="AF7" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -2241,10 +2241,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT7" t="n">
         <v>6.6</v>
@@ -2256,7 +2256,7 @@
         <v>14</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX7" t="n">
         <v>13</v>
@@ -2268,25 +2268,25 @@
         <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD7" t="n">
         <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
         <v>24</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH7" t="n">
         <v>2.94</v>
@@ -2319,7 +2319,7 @@
         <v>7.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
         <v>9.4</v>
@@ -2337,7 +2337,7 @@
         <v>9</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -2384,73 +2384,73 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P8" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
         <v>21</v>
@@ -2459,73 +2459,73 @@
         <v>75</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
         <v>90</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AS8" t="n">
         <v>4.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW8" t="n">
         <v>4.8</v>
       </c>
       <c r="AX8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY8" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB8" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC8" t="n">
         <v>20</v>
@@ -2537,64 +2537,64 @@
         <v>5</v>
       </c>
       <c r="BF8" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BG8" t="n">
         <v>4.9</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP8" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BT8" t="n">
         <v>8</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G9" t="n">
         <v>2.18</v>
@@ -2650,10 +2650,10 @@
         <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
         <v>1.11</v>
@@ -2767,13 +2767,13 @@
         <v>5</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
         <v>5</v>
@@ -2785,13 +2785,13 @@
         <v>5.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE9" t="n">
         <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BG9" t="n">
         <v>5.1</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="G2" t="n">
         <v>1.26</v>
@@ -866,43 +866,43 @@
         <v>14.5</v>
       </c>
       <c r="I2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="S2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
@@ -914,7 +914,7 @@
         <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Z2" t="n">
         <v>180</v>
@@ -923,58 +923,58 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AD2" t="n">
         <v>85</v>
       </c>
       <c r="AE2" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AF2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AK2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>42</v>
+        <v>9.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
         <v>9.199999999999999</v>
@@ -983,49 +983,49 @@
         <v>13</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK2" t="n">
         <v>10</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>2.96</v>
       </c>
       <c r="BN2" t="n">
         <v>3.9</v>
@@ -1046,31 +1046,31 @@
         <v>7</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
         <v>22</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BU2" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>2.94</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 12:56:33</t>
+          <t>2026-06-29 15:03:30</t>
         </is>
       </c>
     </row>
@@ -1111,67 +1111,67 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="G3" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>7.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
         <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="X3" t="n">
         <v>36</v>
       </c>
       <c r="Y3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1183,22 +1183,22 @@
         <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ3" t="n">
         <v>970</v>
@@ -1207,10 +1207,10 @@
         <v>970</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN3" t="n">
         <v>5.7</v>
@@ -1219,112 +1219,112 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT3" t="n">
         <v>3.9</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW3" t="n">
         <v>4</v>
       </c>
-      <c r="AR3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV3" t="n">
+      <c r="AX3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG3" t="n">
         <v>4</v>
       </c>
-      <c r="AW3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY3" t="n">
+      <c r="BH3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI3" t="n">
         <v>3.7</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 12:56:33</t>
+          <t>2026-06-29 15:03:30</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="K4" t="n">
         <v>3.15</v>
@@ -1389,7 +1389,7 @@
         <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.68</v>
@@ -1398,7 +1398,7 @@
         <v>1.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
@@ -1422,10 +1422,10 @@
         <v>7.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
         <v>50</v>
@@ -1434,10 +1434,10 @@
         <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
         <v>55</v>
@@ -1446,7 +1446,7 @@
         <v>29</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
         <v>34</v>
@@ -1473,58 +1473,58 @@
         <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX4" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="AY4" t="n">
         <v>4.5</v>
       </c>
-      <c r="AY4" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH4" t="n">
         <v>2.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 12:56:33</t>
+          <t>2026-06-29 15:03:30</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.74</v>
+        <v>3.7</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="K5" t="n">
         <v>3.2</v>
@@ -1643,142 +1643,142 @@
         <v>1.14</v>
       </c>
       <c r="N5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.28</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
         <v>7.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="Z5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG5" t="n">
         <v>21</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>18</v>
       </c>
       <c r="AH5" t="n">
         <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AJ5" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AL5" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AM5" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AN5" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AO5" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="AP5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA5" t="n">
         <v>6</v>
       </c>
-      <c r="AR5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="BB5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC5" t="n">
         <v>6</v>
       </c>
-      <c r="AU5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5</v>
-      </c>
       <c r="BD5" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BH5" t="n">
         <v>2.58</v>
@@ -1787,62 +1787,62 @@
         <v>2.08</v>
       </c>
       <c r="BJ5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.95</v>
+        <v>8</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BR5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.91</v>
+        <v>7.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="BV5" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.91</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.91</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 12:56:33</t>
+          <t>2026-06-29 15:03:30</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1879,16 @@
         <v>1.63</v>
       </c>
       <c r="H6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.46</v>
@@ -1915,7 +1915,7 @@
         <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
         <v>1.68</v>
@@ -1924,7 +1924,7 @@
         <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X6" t="n">
         <v>14</v>
@@ -1951,7 +1951,7 @@
         <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
@@ -1966,7 +1966,7 @@
         <v>18</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
         <v>65</v>
@@ -1975,22 +1975,22 @@
         <v>270</v>
       </c>
       <c r="AN6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO6" t="n">
         <v>360</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
         <v>5.5</v>
@@ -2002,19 +2002,19 @@
         <v>4.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX6" t="n">
         <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB6" t="n">
         <v>12.5</v>
@@ -2026,13 +2026,13 @@
         <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="n">
         <v>3.2</v>
@@ -2044,19 +2044,19 @@
         <v>13</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO6" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BP6" t="n">
         <v>11.5</v>
@@ -2068,7 +2068,7 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT6" t="n">
         <v>11.5</v>
@@ -2080,13 +2080,13 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 12:56:33</t>
+          <t>2026-06-29 15:03:30</t>
         </is>
       </c>
     </row>
@@ -2127,91 +2127,91 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
         <v>1.47</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
         <v>2.34</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="U7" t="n">
         <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="X7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC7" t="n">
         <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
         <v>60</v>
       </c>
       <c r="AF7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
         <v>80</v>
@@ -2226,13 +2226,13 @@
         <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AO7" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP7" t="n">
         <v>8.6</v>
@@ -2241,10 +2241,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT7" t="n">
         <v>6.6</v>
@@ -2253,43 +2253,43 @@
         <v>6</v>
       </c>
       <c r="AV7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX7" t="n">
         <v>14</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17</v>
+        <v>7.6</v>
       </c>
       <c r="BA7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB7" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB7" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BC7" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD7" t="n">
         <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
-        <v>24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BI7" t="n">
         <v>2.6</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN7" t="n">
         <v>5.2</v>
@@ -2316,13 +2316,13 @@
         <v>21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
         <v>6.8</v>
@@ -2331,26 +2331,26 @@
         <v>4.8</v>
       </c>
       <c r="BV7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW7" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 12:56:33</t>
+          <t>2026-06-29 15:03:30</t>
         </is>
       </c>
     </row>
@@ -2381,73 +2381,73 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="G8" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="H8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.8</v>
       </c>
-      <c r="I8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
         <v>1.42</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="T8" t="n">
         <v>1.93</v>
       </c>
       <c r="U8" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA8" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
         <v>8.6</v>
@@ -2456,10 +2456,10 @@
         <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
@@ -2468,133 +2468,133 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.4</v>
+        <v>3.65</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="AR8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW8" t="n">
         <v>5</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AX8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD8" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BE8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BP8" t="n">
         <v>20</v>
       </c>
-      <c r="BD8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>18</v>
-      </c>
       <c r="BQ8" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS8" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BT8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW8" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 12:56:33</t>
+          <t>2026-06-29 15:03:30</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G9" t="n">
         <v>2.18</v>
@@ -2644,52 +2644,52 @@
         <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K9" t="n">
         <v>3.35</v>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="O9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W9" t="n">
         <v>1.84</v>
       </c>
       <c r="X9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y9" t="n">
         <v>15</v>
@@ -2701,10 +2701,10 @@
         <v>170</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>26</v>
@@ -2716,7 +2716,7 @@
         <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
         <v>29</v>
@@ -2728,25 +2728,25 @@
         <v>32</v>
       </c>
       <c r="AK9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN9" t="n">
         <v>34</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>32</v>
       </c>
       <c r="AO9" t="n">
         <v>180</v>
       </c>
       <c r="AP9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
         <v>4.8</v>
@@ -2755,13 +2755,13 @@
         <v>5.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW9" t="n">
         <v>5</v>
@@ -2770,22 +2770,22 @@
         <v>9.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC9" t="n">
         <v>5</v>
       </c>
-      <c r="BB9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
         <v>5.1</v>
@@ -2797,25 +2797,25 @@
         <v>5.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ9" t="n">
         <v>12.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>3.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO9" t="n">
         <v>3.65</v>
@@ -2827,7 +2827,7 @@
         <v>6.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS9" t="n">
         <v>8.4</v>
@@ -2842,13 +2842,13 @@
         <v>55</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 12:56:33</t>
+          <t>2026-06-29 15:03:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -863,7 +863,7 @@
         <v>1.26</v>
       </c>
       <c r="H2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
         <v>17</v>
@@ -890,7 +890,7 @@
         <v>2.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
         <v>1.81</v>
@@ -899,7 +899,7 @@
         <v>2.06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U2" t="n">
         <v>1.88</v>
@@ -908,7 +908,7 @@
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X2" t="n">
         <v>40</v>
@@ -941,7 +941,7 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI2" t="n">
         <v>180</v>
@@ -983,7 +983,7 @@
         <v>13</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
         <v>10.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>
@@ -1111,55 +1111,55 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="G3" t="n">
         <v>1.39</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I3" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="K3" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.67</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V3" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
         <v>3.55</v>
@@ -1168,10 +1168,10 @@
         <v>36</v>
       </c>
       <c r="Y3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Z3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1183,10 +1183,10 @@
         <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AE3" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AF3" t="n">
         <v>12</v>
@@ -1198,7 +1198,7 @@
         <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
         <v>970</v>
@@ -1216,73 +1216,73 @@
         <v>5.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT3" t="n">
         <v>3.95</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.9</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
       </c>
       <c r="AV3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>4.5</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="BA3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4</v>
       </c>
-      <c r="AX3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BD3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,10 +1291,10 @@
         <v>1.76</v>
       </c>
       <c r="BN3" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1312,13 +1312,13 @@
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>
@@ -1377,19 +1377,19 @@
         <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="K4" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="L4" t="n">
         <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O4" t="n">
         <v>1.68</v>
@@ -1398,7 +1398,7 @@
         <v>1.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
@@ -1407,7 +1407,7 @@
         <v>6.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
         <v>1.59</v>
@@ -1428,28 +1428,28 @@
         <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB4" t="n">
         <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF4" t="n">
         <v>29</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
         <v>110</v>
@@ -1473,58 +1473,58 @@
         <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AQ4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX4" t="n">
         <v>5.2</v>
       </c>
-      <c r="AR4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="AY4" t="n">
         <v>4.8</v>
       </c>
-      <c r="AY4" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH4" t="n">
         <v>2.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>
@@ -1619,25 +1619,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="J5" t="n">
         <v>2.72</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="M5" t="n">
         <v>1.14</v>
@@ -1649,7 +1649,7 @@
         <v>1.6</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q5" t="n">
         <v>2.8</v>
@@ -1658,16 +1658,16 @@
         <v>1.13</v>
       </c>
       <c r="S5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
         <v>1.27</v>
@@ -1682,7 +1682,7 @@
         <v>14.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB5" t="n">
         <v>11</v>
@@ -1691,7 +1691,7 @@
         <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>42</v>
@@ -1712,7 +1712,7 @@
         <v>130</v>
       </c>
       <c r="AK5" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AL5" t="n">
         <v>140</v>
@@ -1724,67 +1724,67 @@
         <v>170</v>
       </c>
       <c r="AO5" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP5" t="n">
         <v>5.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR5" t="n">
         <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
         <v>14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC5" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC5" t="n">
-        <v>6</v>
-      </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF5" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF5" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="BJ5" t="n">
         <v>14</v>
@@ -1796,13 +1796,13 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BN5" t="n">
         <v>8</v>
       </c>
-      <c r="BN5" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BO5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP5" t="n">
         <v>55</v>
@@ -1817,32 +1817,32 @@
         <v>7.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BV5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX5" t="n">
         <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
         <v>75</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G6" t="n">
         <v>1.63</v>
@@ -1987,7 +1987,7 @@
         <v>17</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS6" t="n">
         <v>4.4</v>
@@ -1999,7 +1999,7 @@
         <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW6" t="n">
         <v>4.4</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="G7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
         <v>3.6</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J7" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.45</v>
@@ -2151,67 +2151,67 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="T7" t="n">
         <v>1.93</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X7" t="n">
         <v>10</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA7" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AB7" t="n">
         <v>8.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE7" t="n">
         <v>60</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI7" t="n">
         <v>80</v>
@@ -2229,10 +2229,10 @@
         <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AO7" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP7" t="n">
         <v>8.6</v>
@@ -2244,7 +2244,7 @@
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
         <v>6.6</v>
@@ -2265,28 +2265,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC7" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BD7" t="n">
         <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH7" t="n">
         <v>2.9</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN7" t="n">
         <v>5.2</v>
@@ -2319,10 +2319,10 @@
         <v>8.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT7" t="n">
         <v>6.8</v>
@@ -2334,13 +2334,13 @@
         <v>32</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX7" t="n">
         <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ7" t="n">
         <v>42</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>
@@ -2381,220 +2381,220 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="G8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N8" t="n">
         <v>2.42</v>
       </c>
-      <c r="H8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="O8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S8" t="n">
         <v>5.3</v>
       </c>
-      <c r="J8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.65</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.69</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.7</v>
-      </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
         <v>130</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF8" t="n">
         <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AO8" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.35</v>
+        <v>5.7</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.35</v>
+        <v>5.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BA8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB8" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="BJ8" t="n">
         <v>13</v>
       </c>
       <c r="BK8" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="BP8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
         <v>5.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
         <v>1.68</v>
@@ -2782,7 +2782,7 @@
         <v>21</v>
       </c>
       <c r="BC9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD9" t="n">
         <v>4.9</v>
@@ -2791,7 +2791,7 @@
         <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>20</v>
+        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
         <v>5.1</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -860,10 +860,10 @@
         <v>1.23</v>
       </c>
       <c r="G2" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I2" t="n">
         <v>17</v>
@@ -875,19 +875,19 @@
         <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
         <v>1.42</v>
@@ -896,10 +896,10 @@
         <v>1.81</v>
       </c>
       <c r="S2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
         <v>1.88</v>
@@ -908,7 +908,7 @@
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="X2" t="n">
         <v>40</v>
@@ -923,7 +923,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC2" t="n">
         <v>17</v>
@@ -965,16 +965,16 @@
         <v>310</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT2" t="n">
         <v>9.199999999999999</v>
@@ -983,10 +983,10 @@
         <v>13</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
         <v>8.4</v>
@@ -998,7 +998,7 @@
         <v>27</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="n">
         <v>8.800000000000001</v>
@@ -1007,22 +1007,22 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
         <v>3.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ2" t="n">
         <v>13</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BN2" t="n">
         <v>3.9</v>
@@ -1043,34 +1043,34 @@
         <v>3.45</v>
       </c>
       <c r="BP2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>11.5</v>
+        <v>2.96</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>1.39</v>
       </c>
       <c r="H3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K3" t="n">
         <v>6.4</v>
@@ -1132,13 +1132,13 @@
         <v>1.22</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
         <v>5.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
         <v>2.7</v>
@@ -1147,28 +1147,28 @@
         <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
         <v>3.55</v>
       </c>
       <c r="X3" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="Y3" t="n">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="Z3" t="n">
         <v>110</v>
@@ -1177,37 +1177,37 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AC3" t="n">
         <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AE3" t="n">
         <v>150</v>
       </c>
       <c r="AF3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI3" t="n">
         <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
         <v>970</v>
       </c>
       <c r="AL3" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
         <v>140</v>
@@ -1219,58 +1219,58 @@
         <v>160</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AS3" t="n">
         <v>4.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="AY3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE3" t="n">
         <v>3.95</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
         <v>3.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="n">
         <v>4.9</v>
@@ -1288,16 +1288,16 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ3" t="n">
         <v>5.6</v>
@@ -1306,25 +1306,25 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.73</v>
+        <v>2.24</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.72</v>
+        <v>2.22</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J4" t="n">
         <v>2.64</v>
@@ -1386,7 +1386,7 @@
         <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N4" t="n">
         <v>2.14</v>
@@ -1419,19 +1419,19 @@
         <v>1.31</v>
       </c>
       <c r="X4" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="Z4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>46</v>
+        <v>220</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
         <v>7.6</v>
@@ -1440,10 +1440,10 @@
         <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>48</v>
+        <v>290</v>
       </c>
       <c r="AF4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG4" t="n">
         <v>19.5</v>
@@ -1452,79 +1452,79 @@
         <v>32</v>
       </c>
       <c r="AI4" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AM4" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH4" t="n">
         <v>2.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>2.72</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="L5" t="n">
         <v>1.63</v>
@@ -1643,7 +1643,7 @@
         <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
         <v>1.6</v>
@@ -1655,37 +1655,37 @@
         <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S5" t="n">
         <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U5" t="n">
         <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
         <v>7.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
         <v>7.8</v>
@@ -1694,52 +1694,52 @@
         <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI5" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AJ5" t="n">
         <v>130</v>
       </c>
       <c r="AK5" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AL5" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AM5" t="n">
         <v>320</v>
       </c>
       <c r="AN5" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AO5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
         <v>6</v>
@@ -1748,43 +1748,43 @@
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AY5" t="n">
         <v>14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BH5" t="n">
         <v>2.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="BJ5" t="n">
         <v>14</v>
@@ -1799,10 +1799,10 @@
         <v>7.8</v>
       </c>
       <c r="BN5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP5" t="n">
         <v>55</v>
@@ -1820,10 +1820,10 @@
         <v>5.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BV5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW5" t="n">
         <v>6</v>
@@ -1835,14 +1835,14 @@
         <v>7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
         <v>7.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.46</v>
@@ -1903,22 +1903,22 @@
         <v>1.41</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U6" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
         <v>1.12</v>
@@ -1930,16 +1930,16 @@
         <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="AA6" t="n">
         <v>390</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AC6" t="n">
         <v>11.5</v>
@@ -1951,31 +1951,31 @@
         <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
-        <v>190</v>
+        <v>450</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK6" t="n">
         <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AM6" t="n">
-        <v>270</v>
+        <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO6" t="n">
         <v>360</v>
@@ -1987,10 +1987,10 @@
         <v>17</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT6" t="n">
         <v>5.5</v>
@@ -1999,10 +1999,10 @@
         <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX6" t="n">
         <v>7</v>
@@ -2014,7 +2014,7 @@
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB6" t="n">
         <v>12.5</v>
@@ -2023,16 +2023,16 @@
         <v>17</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH6" t="n">
         <v>3.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>2.32</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>3.2</v>
@@ -2151,37 +2151,37 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="U7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
         <v>12.5</v>
@@ -2190,25 +2190,25 @@
         <v>28</v>
       </c>
       <c r="AA7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7" t="n">
         <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
         <v>60</v>
       </c>
       <c r="AF7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
         <v>19.5</v>
@@ -2244,7 +2244,7 @@
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
         <v>6.6</v>
@@ -2265,28 +2265,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD7" t="n">
         <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
         <v>22</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7" t="n">
         <v>2.9</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN7" t="n">
         <v>5.2</v>
@@ -2313,7 +2313,7 @@
         <v>4.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ7" t="n">
         <v>8.4</v>
@@ -2334,7 +2334,7 @@
         <v>32</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
         <v>55</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>2.08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="H8" t="n">
         <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J8" t="n">
         <v>2.88</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.54</v>
@@ -2405,10 +2405,10 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P8" t="n">
         <v>1.47</v>
@@ -2432,7 +2432,7 @@
         <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X8" t="n">
         <v>9.199999999999999</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H9" t="n">
         <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
         <v>2.84</v>
@@ -2653,46 +2653,46 @@
         <v>3.35</v>
       </c>
       <c r="L9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
         <v>2.46</v>
       </c>
       <c r="O9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R9" t="n">
         <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V9" t="n">
         <v>1.21</v>
       </c>
       <c r="W9" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="X9" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
         <v>42</v>
@@ -2701,7 +2701,7 @@
         <v>170</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC9" t="n">
         <v>8.199999999999999</v>
@@ -2722,7 +2722,7 @@
         <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ9" t="n">
         <v>32</v>
@@ -2731,13 +2731,13 @@
         <v>36</v>
       </c>
       <c r="AL9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM9" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO9" t="n">
         <v>180</v>
@@ -2749,10 +2749,10 @@
         <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT9" t="n">
         <v>5.5</v>
@@ -2764,7 +2764,7 @@
         <v>18.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX9" t="n">
         <v>9.4</v>
@@ -2776,37 +2776,37 @@
         <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB9" t="n">
         <v>21</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2821,7 +2821,7 @@
         <v>3.65</v>
       </c>
       <c r="BP9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ9" t="n">
         <v>6.6</v>
@@ -2830,7 +2830,7 @@
         <v>46</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT9" t="n">
         <v>8.199999999999999</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G2" t="n">
         <v>1.23</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.24</v>
       </c>
       <c r="H2" t="n">
         <v>15.5</v>
@@ -869,10 +869,10 @@
         <v>17</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>1.21</v>
@@ -893,7 +893,7 @@
         <v>1.42</v>
       </c>
       <c r="R2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S2" t="n">
         <v>2.04</v>
@@ -908,13 +908,13 @@
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="X2" t="n">
         <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Z2" t="n">
         <v>180</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AD2" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AE2" t="n">
         <v>260</v>
@@ -941,7 +941,7 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
         <v>180</v>
@@ -950,7 +950,7 @@
         <v>10.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AL2" t="n">
         <v>36</v>
@@ -965,40 +965,40 @@
         <v>310</v>
       </c>
       <c r="AP2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AV2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX2" t="n">
         <v>8.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>27</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
         <v>8.800000000000001</v>
@@ -1007,10 +1007,10 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
         <v>3.1</v>
@@ -1028,13 +1028,13 @@
         <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="BN2" t="n">
         <v>3.9</v>
@@ -1046,31 +1046,31 @@
         <v>6.8</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BR2" t="n">
         <v>21</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="BT2" t="n">
         <v>17.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>3</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.96</v>
+        <v>12</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>1.36</v>
       </c>
       <c r="G3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
         <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
@@ -1147,16 +1147,16 @@
         <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
         <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V3" t="n">
         <v>1.1</v>
@@ -1177,7 +1177,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AC3" t="n">
         <v>970</v>
@@ -1192,7 +1192,7 @@
         <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH3" t="n">
         <v>75</v>
@@ -1204,7 +1204,7 @@
         <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
@@ -1213,19 +1213,19 @@
         <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>5.7</v>
+        <v>15</v>
       </c>
       <c r="AO3" t="n">
         <v>160</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AS3" t="n">
         <v>4.2</v>
@@ -1237,7 +1237,7 @@
         <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AW3" t="n">
         <v>4.2</v>
@@ -1249,7 +1249,7 @@
         <v>6.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
         <v>4.2</v>
@@ -1261,28 +1261,28 @@
         <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="BF3" t="n">
         <v>3.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="n">
         <v>4.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,40 +1291,40 @@
         <v>2.26</v>
       </c>
       <c r="BN3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>5.5</v>
       </c>
-      <c r="BO3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.6</v>
+        <v>2.06</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.24</v>
+        <v>4.7</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G4" t="n">
         <v>4.2</v>
@@ -1380,7 +1380,7 @@
         <v>2.64</v>
       </c>
       <c r="K4" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.61</v>
@@ -1398,7 +1398,7 @@
         <v>1.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
@@ -1422,7 +1422,7 @@
         <v>7</v>
       </c>
       <c r="Y4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="Z4" t="n">
         <v>15.5</v>
@@ -1473,7 +1473,7 @@
         <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AQ4" t="n">
         <v>3.85</v>
@@ -1482,7 +1482,7 @@
         <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AT4" t="n">
         <v>4.9</v>
@@ -1491,40 +1491,40 @@
         <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AW4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA4" t="n">
         <v>7</v>
       </c>
-      <c r="AX4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BB4" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="n">
         <v>2.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>
@@ -1619,40 +1619,40 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="J5" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.6</v>
       </c>
       <c r="P5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="R5" t="n">
         <v>1.14</v>
@@ -1667,40 +1667,40 @@
         <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5" t="n">
         <v>7</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
         <v>30</v>
@@ -1709,7 +1709,7 @@
         <v>200</v>
       </c>
       <c r="AJ5" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
         <v>210</v>
@@ -1718,16 +1718,16 @@
         <v>540</v>
       </c>
       <c r="AM5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.5</v>
@@ -1739,16 +1739,16 @@
         <v>14.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
         <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="AX5" t="n">
         <v>11.5</v>
@@ -1760,89 +1760,89 @@
         <v>6.4</v>
       </c>
       <c r="BA5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB5" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BC5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE5" t="n">
         <v>7</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BF5" t="n">
         <v>7</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7.2</v>
       </c>
       <c r="BG5" t="n">
         <v>8.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="BJ5" t="n">
         <v>14</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BW5" t="n">
         <v>6</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
         <v>2.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
         <v>4.4</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>
@@ -2133,16 +2133,16 @@
         <v>2.44</v>
       </c>
       <c r="H7" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
         <v>1.45</v>
@@ -2154,7 +2154,7 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
         <v>1.68</v>
@@ -2169,7 +2169,7 @@
         <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
         <v>1.94</v>
@@ -2187,10 +2187,10 @@
         <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="n">
         <v>8.199999999999999</v>
@@ -2199,13 +2199,13 @@
         <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG7" t="n">
         <v>11.5</v>
@@ -2214,25 +2214,25 @@
         <v>19.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM7" t="n">
         <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP7" t="n">
         <v>8.6</v>
@@ -2241,13 +2241,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
         <v>6</v>
@@ -2256,37 +2256,37 @@
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BA7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD7" t="n">
         <v>10</v>
       </c>
-      <c r="BB7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>38</v>
-      </c>
       <c r="BE7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG7" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BH7" t="n">
         <v>2.9</v>
@@ -2298,7 +2298,7 @@
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2337,20 +2337,20 @@
         <v>10</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>11</v>
       </c>
       <c r="BZ7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
         <v>10.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="H8" t="n">
         <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K8" t="n">
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
@@ -2408,31 +2408,31 @@
         <v>2.44</v>
       </c>
       <c r="O8" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="R8" t="n">
         <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="X8" t="n">
         <v>9.199999999999999</v>
@@ -2459,25 +2459,25 @@
         <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
         <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK8" t="n">
         <v>36</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM8" t="n">
         <v>240</v>
@@ -2486,31 +2486,31 @@
         <v>36</v>
       </c>
       <c r="AO8" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
         <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW8" t="n">
         <v>5.9</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.5</v>
       </c>
       <c r="AX8" t="n">
         <v>9.199999999999999</v>
@@ -2519,28 +2519,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH8" t="n">
         <v>2.84</v>
@@ -2552,13 +2552,13 @@
         <v>13</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BN8" t="n">
         <v>5.1</v>
@@ -2570,31 +2570,31 @@
         <v>21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G9" t="n">
         <v>2.22</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
         <v>5.6</v>
@@ -2668,7 +2668,7 @@
         <v>1.49</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.17</v>
@@ -2686,7 +2686,7 @@
         <v>1.21</v>
       </c>
       <c r="W9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X9" t="n">
         <v>9</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 19:17:42</t>
+          <t>2026-06-29 21:24:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -965,10 +965,10 @@
         <v>310</v>
       </c>
       <c r="AP2" t="n">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AR2" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
         <v>14.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
         <v>10.5</v>
@@ -998,7 +998,7 @@
         <v>27</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB2" t="n">
         <v>8.800000000000001</v>
@@ -1007,10 +1007,10 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF2" t="n">
         <v>3.1</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="BN2" t="n">
         <v>3.9</v>
@@ -1052,25 +1052,25 @@
         <v>21</v>
       </c>
       <c r="BS2" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BT2" t="n">
         <v>17.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>3</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>12</v>
+        <v>2.96</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>1.38</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I3" t="n">
         <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
@@ -1141,7 +1141,7 @@
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q3" t="n">
         <v>1.5</v>
@@ -1150,7 +1150,7 @@
         <v>1.68</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
         <v>1.87</v>
@@ -1162,7 +1162,7 @@
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="X3" t="n">
         <v>70</v>
@@ -1171,13 +1171,13 @@
         <v>160</v>
       </c>
       <c r="Z3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
         <v>970</v>
@@ -1219,10 +1219,10 @@
         <v>160</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR3" t="n">
         <v>4.2</v>
@@ -1249,7 +1249,7 @@
         <v>6.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA3" t="n">
         <v>4.2</v>
@@ -1261,28 +1261,28 @@
         <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH3" t="n">
         <v>4.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,13 +1291,13 @@
         <v>2.26</v>
       </c>
       <c r="BN3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BQ3" t="n">
         <v>5.5</v>
@@ -1306,7 +1306,7 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.06</v>
+        <v>6.6</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,7 +1318,7 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>
@@ -1371,16 +1371,16 @@
         <v>4.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I4" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J4" t="n">
         <v>2.64</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="L4" t="n">
         <v>1.61</v>
@@ -1491,7 +1491,7 @@
         <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW4" t="n">
         <v>6.6</v>
@@ -1548,7 +1548,7 @@
         <v>7.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1566,7 +1566,7 @@
         <v>5.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>
@@ -1622,88 +1622,88 @@
         <v>4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="H5" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="I5" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K5" t="n">
         <v>3.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.6</v>
       </c>
       <c r="P5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S5" t="n">
         <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="W5" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
         <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
         <v>200</v>
@@ -1724,13 +1724,13 @@
         <v>500</v>
       </c>
       <c r="AO5" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP5" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR5" t="n">
         <v>9.800000000000001</v>
@@ -1760,89 +1760,89 @@
         <v>6.4</v>
       </c>
       <c r="BA5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB5" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BC5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE5" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7</v>
-      </c>
       <c r="BF5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG5" t="n">
         <v>8.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BJ5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT5" t="n">
         <v>5.2</v>
       </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BU5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BV5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BW5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BX5" t="n">
         <v>55</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>65</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T6" t="n">
         <v>2.26</v>
@@ -1942,7 +1942,7 @@
         <v>6.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>38</v>
@@ -1951,7 +1951,7 @@
         <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
@@ -1987,10 +1987,10 @@
         <v>17</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
         <v>5.5</v>
@@ -2002,7 +2002,7 @@
         <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
         <v>7</v>
@@ -2014,7 +2014,7 @@
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
         <v>12.5</v>
@@ -2023,16 +2023,16 @@
         <v>17</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="n">
         <v>3.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>
@@ -2127,79 +2127,79 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X7" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA7" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AC7" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
         <v>55</v>
@@ -2208,149 +2208,149 @@
         <v>16</v>
       </c>
       <c r="AG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ7" t="n">
+      <c r="AR7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD7" t="n">
         <v>34</v>
       </c>
-      <c r="AK7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD7" t="n">
+      <c r="BE7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>10</v>
       </c>
-      <c r="BE7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ7" t="n">
+      <c r="BK7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
         <v>11</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>13.5</v>
       </c>
       <c r="BN7" t="n">
         <v>5.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BS7" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BU7" t="n">
         <v>4.8</v>
       </c>
       <c r="BV7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BW7" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA7" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G8" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
         <v>2.86</v>
@@ -2399,49 +2399,49 @@
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="O8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q8" t="n">
         <v>2.48</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V8" t="n">
         <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="X8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="n">
         <v>130</v>
@@ -2450,7 +2450,7 @@
         <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
         <v>21</v>
@@ -2468,97 +2468,97 @@
         <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
         <v>34</v>
       </c>
       <c r="AK8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
         <v>70</v>
       </c>
       <c r="AM8" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP8" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ8" t="n">
         <v>8.6</v>
       </c>
       <c r="AR8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT8" t="n">
         <v>5.9</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BA8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD8" t="n">
         <v>6</v>
       </c>
-      <c r="BB8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF8" t="n">
         <v>6</v>
       </c>
-      <c r="BF8" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG8" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BN8" t="n">
         <v>5.1</v>
@@ -2567,34 +2567,34 @@
         <v>3.75</v>
       </c>
       <c r="BP8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>7</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>1.98</v>
       </c>
       <c r="G9" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
         <v>5.6</v>
@@ -2686,40 +2686,40 @@
         <v>1.21</v>
       </c>
       <c r="W9" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA9" t="n">
         <v>170</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
         <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
         <v>130</v>
@@ -2728,7 +2728,7 @@
         <v>32</v>
       </c>
       <c r="AK9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
         <v>70</v>
@@ -2749,10 +2749,10 @@
         <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT9" t="n">
         <v>5.5</v>
@@ -2764,7 +2764,7 @@
         <v>18.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX9" t="n">
         <v>9.4</v>
@@ -2776,25 +2776,25 @@
         <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
         <v>21</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF9" t="n">
         <v>21</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH9" t="n">
         <v>2.72</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 21:24:22</t>
+          <t>2026-06-29 23:30:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -857,82 +857,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="H2" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R2" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="S2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="X2" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="Y2" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="Z2" t="n">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>55</v>
+        <v>320</v>
       </c>
       <c r="AE2" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="AF2" t="n">
         <v>10</v>
@@ -941,13 +941,13 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AI2" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AK2" t="n">
         <v>15.5</v>
@@ -956,34 +956,34 @@
         <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>310</v>
+        <v>400</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="AQ2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS2" t="n">
         <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>9.4</v>
       </c>
       <c r="AW2" t="n">
         <v>10.5</v>
@@ -1001,76 +1001,76 @@
         <v>10.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BE2" t="n">
         <v>10.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="BG2" t="n">
         <v>15</v>
       </c>
       <c r="BH2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO2" t="n">
         <v>3.45</v>
       </c>
       <c r="BP2" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BR2" t="n">
         <v>21</v>
       </c>
       <c r="BS2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU2" t="n">
         <v>8.4</v>
       </c>
-      <c r="BT2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.96</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G3" t="n">
         <v>1.38</v>
@@ -1123,46 +1123,46 @@
         <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="K3" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="T3" t="n">
         <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="X3" t="n">
         <v>70</v>
@@ -1171,130 +1171,130 @@
         <v>160</v>
       </c>
       <c r="Z3" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AD3" t="n">
         <v>120</v>
       </c>
       <c r="AE3" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AF3" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AI3" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>17.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>230</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG3" t="n">
         <v>15</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>8.4</v>
       </c>
       <c r="BH3" t="n">
         <v>4.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.26</v>
+        <v>7</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BP3" t="n">
         <v>7.8</v>
@@ -1306,7 +1306,7 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,13 +1318,13 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.02</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>
@@ -1365,94 +1365,94 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2.78</v>
+        <v>7.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="K4" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="O4" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>1.64</v>
       </c>
       <c r="R4" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.8</v>
+        <v>1.65</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
         <v>220</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
         <v>290</v>
       </c>
       <c r="AF4" t="n">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="AG4" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ4" t="n">
         <v>500</v>
@@ -1473,7 +1473,7 @@
         <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>3.85</v>
@@ -1482,113 +1482,113 @@
         <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>1.93</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.9</v>
+        <v>1.91</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.9</v>
+        <v>1.87</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>1.87</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="BC4" t="n">
-        <v>7</v>
+        <v>1.93</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.2</v>
+        <v>1.96</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>1.96</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.2</v>
+        <v>1.96</v>
       </c>
       <c r="BG4" t="n">
         <v>9</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="n">
         <v>2.4</v>
@@ -1634,37 +1634,37 @@
         <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
         <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R5" t="n">
         <v>1.15</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
         <v>1.71</v>
@@ -1673,7 +1673,7 @@
         <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Y5" t="n">
         <v>7.4</v>
@@ -1697,13 +1697,13 @@
         <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
         <v>200</v>
@@ -1715,7 +1715,7 @@
         <v>210</v>
       </c>
       <c r="AL5" t="n">
-        <v>540</v>
+        <v>260</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
@@ -1727,19 +1727,19 @@
         <v>42</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS5" t="n">
         <v>14.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU5" t="n">
         <v>6</v>
@@ -1754,10 +1754,10 @@
         <v>11.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
         <v>6.4</v>
@@ -1766,7 +1766,7 @@
         <v>6.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
         <v>6.6</v>
@@ -1775,7 +1775,7 @@
         <v>6.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG5" t="n">
         <v>8.4</v>
@@ -1784,65 +1784,65 @@
         <v>2.68</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BJ5" t="n">
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BN5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT5" t="n">
         <v>5.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV5" t="n">
         <v>23</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX5" t="n">
         <v>55</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>65</v>
       </c>
       <c r="CA5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>
@@ -1873,220 +1873,220 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.41</v>
       </c>
       <c r="P6" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.24</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.26</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
         <v>2.58</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="n">
         <v>270</v>
       </c>
       <c r="AA6" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE6" t="n">
         <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AI6" t="n">
         <v>450</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="AM6" t="n">
         <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO6" t="n">
         <v>360</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT6" t="n">
         <v>5.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
         <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
         <v>17</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BJ6" t="n">
         <v>13</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BP6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BT6" t="n">
         <v>11.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G7" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
         <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
         <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
         <v>2.08</v>
@@ -2178,10 +2178,10 @@
         <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
         <v>14</v>
@@ -2193,10 +2193,10 @@
         <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD7" t="n">
         <v>16</v>
@@ -2211,7 +2211,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI7" t="n">
         <v>80</v>
@@ -2220,7 +2220,7 @@
         <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
@@ -2229,7 +2229,7 @@
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
         <v>60</v>
@@ -2244,13 +2244,13 @@
         <v>22</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
         <v>8.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
         <v>12.5</v>
@@ -2265,7 +2265,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA7" t="n">
         <v>44</v>
@@ -2274,13 +2274,13 @@
         <v>22</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
         <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF7" t="n">
         <v>18.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="H8" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
         <v>1.71</v>
       </c>
       <c r="V8" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="X8" t="n">
         <v>9.199999999999999</v>
@@ -2441,7 +2441,7 @@
         <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
         <v>130</v>
@@ -2459,7 +2459,7 @@
         <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
         <v>13.5</v>
@@ -2468,25 +2468,25 @@
         <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
         <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AN8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO8" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP8" t="n">
         <v>6.6</v>
@@ -2495,13 +2495,13 @@
         <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
         <v>6.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
@@ -2522,7 +2522,7 @@
         <v>5.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB8" t="n">
         <v>21</v>
@@ -2531,7 +2531,7 @@
         <v>21</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE8" t="n">
         <v>6.4</v>
@@ -2543,25 +2543,25 @@
         <v>6.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ8" t="n">
         <v>12.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO8" t="n">
         <v>3.75</v>
@@ -2570,16 +2570,16 @@
         <v>20</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BU8" t="n">
         <v>5.8</v>
@@ -2588,13 +2588,13 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>
@@ -2635,46 +2635,46 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I9" t="n">
         <v>5.1</v>
       </c>
-      <c r="I9" t="n">
-        <v>5.6</v>
-      </c>
       <c r="J9" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="L9" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="O9" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="P9" t="n">
         <v>1.49</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
         <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T9" t="n">
         <v>2.18</v>
@@ -2683,22 +2683,22 @@
         <v>1.69</v>
       </c>
       <c r="V9" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="X9" t="n">
         <v>8.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA9" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AB9" t="n">
         <v>6.8</v>
@@ -2707,22 +2707,22 @@
         <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ9" t="n">
         <v>32</v>
@@ -2740,19 +2740,19 @@
         <v>32</v>
       </c>
       <c r="AO9" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP9" t="n">
         <v>6.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
         <v>5.5</v>
@@ -2761,10 +2761,10 @@
         <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX9" t="n">
         <v>9.4</v>
@@ -2776,7 +2776,7 @@
         <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB9" t="n">
         <v>21</v>
@@ -2785,16 +2785,16 @@
         <v>22</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9" t="n">
         <v>21</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BH9" t="n">
         <v>2.72</v>
@@ -2803,7 +2803,7 @@
         <v>2.22</v>
       </c>
       <c r="BJ9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK9" t="n">
         <v>5.7</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
         <v>4.8</v>
@@ -2830,7 +2830,7 @@
         <v>46</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT9" t="n">
         <v>8.199999999999999</v>
@@ -2842,13 +2842,13 @@
         <v>55</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 23:30:59</t>
+          <t>2026-06-30 01:37:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="G2" t="n">
         <v>1.21</v>
@@ -872,7 +872,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
@@ -881,7 +881,7 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
@@ -890,34 +890,34 @@
         <v>3.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
         <v>1.87</v>
       </c>
       <c r="S2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X2" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
         <v>420</v>
       </c>
       <c r="Z2" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -932,10 +932,10 @@
         <v>320</v>
       </c>
       <c r="AE2" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -944,76 +944,76 @@
         <v>40</v>
       </c>
       <c r="AI2" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
         <v>210</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AO2" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="AP2" t="n">
         <v>32</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.4</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BG2" t="n">
         <v>15</v>
@@ -1025,7 +1025,7 @@
         <v>4.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK2" t="n">
         <v>7.2</v>
@@ -1034,13 +1034,13 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP2" t="n">
         <v>6.4</v>
@@ -1052,25 +1052,25 @@
         <v>21</v>
       </c>
       <c r="BS2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2" t="n">
         <v>18.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY2" t="n">
         <v>14</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>13.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H3" t="n">
         <v>9.4</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="K3" t="n">
         <v>6</v>
@@ -1138,7 +1138,7 @@
         <v>6.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
         <v>2.78</v>
@@ -1147,19 +1147,19 @@
         <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
         <v>3.55</v>
@@ -1168,106 +1168,106 @@
         <v>70</v>
       </c>
       <c r="Y3" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="Z3" t="n">
         <v>130</v>
       </c>
       <c r="AA3" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="AE3" t="n">
         <v>170</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
         <v>260</v>
       </c>
       <c r="AJ3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AL3" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AO3" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AR3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
         <v>46</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BF3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG3" t="n">
         <v>15</v>
@@ -1288,13 +1288,13 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BN3" t="n">
         <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP3" t="n">
         <v>7.8</v>
@@ -1306,25 +1306,25 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>2.92</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="I4" t="n">
         <v>7.2</v>
@@ -1398,7 +1398,7 @@
         <v>1.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R4" t="n">
         <v>1.08</v>
@@ -1428,7 +1428,7 @@
         <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
         <v>970</v>
@@ -1440,7 +1440,7 @@
         <v>18</v>
       </c>
       <c r="AE4" t="n">
-        <v>290</v>
+        <v>110</v>
       </c>
       <c r="AF4" t="n">
         <v>90</v>
@@ -1449,10 +1449,10 @@
         <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AI4" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
         <v>500</v>
@@ -1467,10 +1467,10 @@
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
         <v>3.5</v>
@@ -1482,10 +1482,10 @@
         <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AU4" t="n">
         <v>5.1</v>
@@ -1494,34 +1494,34 @@
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX4" t="n">
         <v>1.9</v>
       </c>
-      <c r="AX4" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>1.88</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BG4" t="n">
         <v>9</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>2.26</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J5" t="n">
         <v>2.9</v>
@@ -1640,73 +1640,73 @@
         <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P5" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
         <v>5.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W5" t="n">
         <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z5" t="n">
         <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
         <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF5" t="n">
         <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
         <v>500</v>
@@ -1721,16 +1721,16 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
         <v>10</v>
@@ -1739,7 +1739,7 @@
         <v>14.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="AU5" t="n">
         <v>6</v>
@@ -1748,16 +1748,16 @@
         <v>9.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
         <v>11.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA5" t="n">
         <v>6.4</v>
@@ -1772,31 +1772,31 @@
         <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
         <v>6.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="BJ5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BN5" t="n">
         <v>7.8</v>
@@ -1805,44 +1805,44 @@
         <v>5.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT5" t="n">
         <v>5.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="BV5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BX5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>1.58</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
@@ -1900,10 +1900,10 @@
         <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
         <v>2.26</v>
@@ -1915,19 +1915,19 @@
         <v>4.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
         <v>2.58</v>
       </c>
       <c r="X6" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
         <v>21</v>
@@ -1936,22 +1936,22 @@
         <v>270</v>
       </c>
       <c r="AA6" t="n">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AB6" t="n">
         <v>6.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AE6" t="n">
         <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
@@ -1963,10 +1963,10 @@
         <v>450</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>140</v>
@@ -1978,34 +1978,34 @@
         <v>12.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="AP6" t="n">
         <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>5.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>8.6</v>
@@ -2014,46 +2014,46 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
       </c>
       <c r="BC6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>11.5</v>
+        <v>2.9</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BO6" t="n">
         <v>3</v>
@@ -2062,31 +2062,31 @@
         <v>11</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BT6" t="n">
         <v>11.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.5</v>
+        <v>2.84</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>2.84</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
         <v>3.15</v>
@@ -2166,7 +2166,7 @@
         <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
         <v>1.83</v>
@@ -2184,7 +2184,7 @@
         <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
         <v>28</v>
@@ -2199,7 +2199,7 @@
         <v>7.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE7" t="n">
         <v>55</v>
@@ -2244,7 +2244,7 @@
         <v>22</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT7" t="n">
         <v>8.6</v>
@@ -2274,13 +2274,13 @@
         <v>22</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD7" t="n">
         <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
         <v>18.5</v>
@@ -2289,7 +2289,7 @@
         <v>38</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI7" t="n">
         <v>2.9</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN7" t="n">
         <v>5.2</v>
@@ -2316,13 +2316,13 @@
         <v>18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR7" t="n">
         <v>34</v>
       </c>
       <c r="BS7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7" t="n">
         <v>7.2</v>
@@ -2334,23 +2334,23 @@
         <v>29</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G8" t="n">
         <v>2.16</v>
@@ -2393,61 +2393,61 @@
         <v>4.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
         <v>1.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
         <v>1.86</v>
       </c>
       <c r="X8" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC8" t="n">
         <v>8</v>
@@ -2456,7 +2456,7 @@
         <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF8" t="n">
         <v>13</v>
@@ -2465,109 +2465,109 @@
         <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK8" t="n">
         <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AN8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>21</v>
+        <v>5.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BD8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF8" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>6</v>
-      </c>
       <c r="BG8" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN8" t="n">
         <v>5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>6.2</v>
@@ -2576,25 +2576,25 @@
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT8" t="n">
         <v>7.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
         <v>2.2</v>
@@ -2644,10 +2644,10 @@
         <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K9" t="n">
         <v>3.15</v>
@@ -2683,7 +2683,7 @@
         <v>1.69</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
         <v>1.83</v>
@@ -2827,7 +2827,7 @@
         <v>6.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
         <v>8.4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -866,22 +866,22 @@
         <v>18.5</v>
       </c>
       <c r="I2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
@@ -893,13 +893,13 @@
         <v>1.42</v>
       </c>
       <c r="R2" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="S2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
         <v>1.87</v>
@@ -911,13 +911,13 @@
         <v>5.7</v>
       </c>
       <c r="X2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y2" t="n">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="Z2" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -926,13 +926,13 @@
         <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AE2" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AF2" t="n">
         <v>10.5</v>
@@ -941,28 +941,28 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI2" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AJ2" t="n">
         <v>9.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
         <v>3.25</v>
       </c>
       <c r="AO2" t="n">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="AP2" t="n">
         <v>32</v>
@@ -974,7 +974,7 @@
         <v>9.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -983,10 +983,10 @@
         <v>16.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX2" t="n">
         <v>8</v>
@@ -995,7 +995,7 @@
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BA2" t="n">
         <v>9.800000000000001</v>
@@ -1013,22 +1013,22 @@
         <v>9.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BG2" t="n">
         <v>15</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BJ2" t="n">
         <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>3.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP2" t="n">
         <v>6.4</v>
@@ -1055,22 +1055,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BX2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H3" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="I3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -1135,94 +1135,94 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="R3" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="T3" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
         <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="X3" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="Y3" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="Z3" t="n">
         <v>130</v>
       </c>
       <c r="AA3" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AB3" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE3" t="n">
         <v>170</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
         <v>260</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AL3" t="n">
         <v>30</v>
       </c>
       <c r="AM3" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AR3" t="n">
         <v>36</v>
@@ -1231,7 +1231,7 @@
         <v>11.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
         <v>12</v>
@@ -1240,34 +1240,34 @@
         <v>28</v>
       </c>
       <c r="AW3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BG3" t="n">
         <v>15</v>
@@ -1288,43 +1288,43 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BP3" t="n">
         <v>7.8</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.2</v>
+        <v>3.35</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>
@@ -1371,13 +1371,13 @@
         <v>7.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="I4" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="K4" t="n">
         <v>2.8</v>
@@ -1395,16 +1395,16 @@
         <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.65</v>
+        <v>2.44</v>
       </c>
       <c r="R4" t="n">
         <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.65</v>
+        <v>6.2</v>
       </c>
       <c r="T4" t="n">
         <v>1.83</v>
@@ -1413,7 +1413,7 @@
         <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
         <v>1.23</v>
@@ -1443,7 +1443,7 @@
         <v>110</v>
       </c>
       <c r="AF4" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
         <v>23</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="I5" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="O5" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="X5" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="n">
         <v>7.6</v>
       </c>
       <c r="Z5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB5" t="n">
         <v>14</v>
       </c>
-      <c r="AA5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>12</v>
-      </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
         <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AF5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AG5" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
         <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>210</v>
+        <v>95</v>
       </c>
       <c r="AL5" t="n">
-        <v>260</v>
+        <v>540</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>600</v>
+        <v>130</v>
       </c>
       <c r="AO5" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AR5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT5" t="n">
         <v>10</v>
       </c>
-      <c r="AS5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
         <v>6.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO5" t="n">
         <v>6</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>5.6</v>
       </c>
       <c r="BP5" t="n">
         <v>48</v>
       </c>
       <c r="BQ5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>65</v>
+      </c>
+      <c r="BS5" t="n">
         <v>6.8</v>
       </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BT5" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BZ5" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="CA5" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>
@@ -1873,85 +1873,85 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="G6" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="Z6" t="n">
         <v>270</v>
       </c>
       <c r="AA6" t="n">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC6" t="n">
         <v>9.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AE6" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
@@ -1966,19 +1966,19 @@
         <v>15</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL6" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM6" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AP6" t="n">
         <v>10</v>
@@ -1993,7 +1993,7 @@
         <v>9</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
@@ -2011,7 +2011,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
         <v>8.800000000000001</v>
@@ -2020,28 +2020,28 @@
         <v>12</v>
       </c>
       <c r="BC6" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD6" t="n">
         <v>7.8</v>
       </c>
       <c r="BE6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF6" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>10.5</v>
       </c>
       <c r="BG6" t="n">
         <v>9</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK6" t="n">
         <v>5.9</v>
@@ -2050,16 +2050,16 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.9</v>
+        <v>11</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BP6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ6" t="n">
         <v>5.6</v>
@@ -2071,7 +2071,7 @@
         <v>8.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU6" t="n">
         <v>5.7</v>
@@ -2080,13 +2080,13 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.84</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.84</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>2.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I7" t="n">
         <v>3.85</v>
@@ -2157,13 +2157,13 @@
         <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q7" t="n">
         <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -2208,7 +2208,7 @@
         <v>16</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
         <v>18</v>
@@ -2244,7 +2244,7 @@
         <v>22</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
         <v>8.6</v>
@@ -2262,7 +2262,7 @@
         <v>13.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
         <v>14.5</v>
@@ -2274,13 +2274,13 @@
         <v>22</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
         <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
         <v>18.5</v>
@@ -2322,7 +2322,7 @@
         <v>34</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT7" t="n">
         <v>7.2</v>
@@ -2334,7 +2334,7 @@
         <v>29</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>
@@ -2381,133 +2381,133 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G8" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="L8" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>2.66</v>
+        <v>2.98</v>
       </c>
       <c r="O8" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
         <v>80</v>
       </c>
-      <c r="AF8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>100</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
         <v>5.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW8" t="n">
         <v>5.7</v>
@@ -2519,16 +2519,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
         <v>5.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.2</v>
+        <v>19</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BD8" t="n">
         <v>5.6</v>
@@ -2537,64 +2537,64 @@
         <v>6</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="BG8" t="n">
         <v>5.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN8" t="n">
         <v>5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP8" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT8" t="n">
         <v>7.6</v>
       </c>
-      <c r="BT8" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BU8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>
@@ -2635,220 +2635,220 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="H9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S9" t="n">
         <v>4.8</v>
       </c>
-      <c r="I9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S9" t="n">
-        <v>6.2</v>
-      </c>
       <c r="T9" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="V9" t="n">
         <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="X9" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
         <v>36</v>
       </c>
       <c r="AA9" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>27</v>
       </c>
-      <c r="AI9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>32</v>
-      </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL9" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="AN9" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AP9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA9" t="n">
+      <c r="BR9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BT9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU9" t="n">
         <v>6</v>
       </c>
       <c r="BV9" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="G2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>1.23</v>
@@ -893,28 +893,28 @@
         <v>1.42</v>
       </c>
       <c r="R2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S2" t="n">
         <v>2.08</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="X2" t="n">
         <v>42</v>
       </c>
       <c r="Y2" t="n">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="Z2" t="n">
         <v>200</v>
@@ -923,16 +923,16 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AE2" t="n">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="AF2" t="n">
         <v>10.5</v>
@@ -941,55 +941,55 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AI2" t="n">
         <v>220</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AN2" t="n">
         <v>3.25</v>
       </c>
       <c r="AO2" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="AP2" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AW2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -998,10 +998,10 @@
         <v>25</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BC2" t="n">
         <v>11.5</v>
@@ -1010,16 +1010,16 @@
         <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="BG2" t="n">
         <v>15</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI2" t="n">
         <v>4.7</v>
@@ -1028,13 +1028,13 @@
         <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN2" t="n">
         <v>3.9</v>
@@ -1043,22 +1043,22 @@
         <v>3.55</v>
       </c>
       <c r="BP2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR2" t="n">
         <v>21</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT2" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1070,7 +1070,7 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>
@@ -1114,31 +1114,31 @@
         <v>1.39</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K3" t="n">
         <v>5.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
         <v>2.88</v>
@@ -1153,109 +1153,109 @@
         <v>2.22</v>
       </c>
       <c r="T3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
         <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="X3" t="n">
         <v>29</v>
       </c>
       <c r="Y3" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="Z3" t="n">
         <v>130</v>
       </c>
       <c r="AA3" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AB3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC3" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="AF3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>13</v>
       </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AK3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AL3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AO3" t="n">
         <v>120</v>
       </c>
       <c r="AP3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AR3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AT3" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AU3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC3" t="n">
         <v>12</v>
@@ -1264,19 +1264,19 @@
         <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG3" t="n">
         <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1288,43 +1288,43 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN3" t="n">
         <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="BT3" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.35</v>
+        <v>8.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>
@@ -1365,46 +1365,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>2.72</v>
       </c>
       <c r="J4" t="n">
         <v>2.76</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="P4" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="R4" t="n">
         <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.2</v>
+        <v>2.54</v>
       </c>
       <c r="T4" t="n">
         <v>1.83</v>
@@ -1413,7 +1413,7 @@
         <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="W4" t="n">
         <v>1.23</v>
@@ -1467,7 +1467,7 @@
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
         <v>600</v>
@@ -1482,7 +1482,7 @@
         <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AT4" t="n">
         <v>1.94</v>
@@ -1494,34 +1494,34 @@
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BB4" t="n">
         <v>1.93</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BC4" t="n">
         <v>1.9</v>
       </c>
-      <c r="AY4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.97</v>
-      </c>
       <c r="BD4" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BE4" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BF4" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BG4" t="n">
         <v>9</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>
@@ -1619,124 +1619,124 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O5" t="n">
         <v>1.52</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.44</v>
-      </c>
       <c r="P5" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="W5" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH5" t="n">
         <v>28</v>
       </c>
-      <c r="AB5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>25</v>
-      </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AK5" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AL5" t="n">
-        <v>540</v>
+        <v>120</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AO5" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1745,52 +1745,52 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>21</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BA5" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG5" t="n">
         <v>13.5</v>
       </c>
-      <c r="AY5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>18</v>
-      </c>
       <c r="BH5" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,19 +1799,19 @@
         <v>7.4</v>
       </c>
       <c r="BN5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO5" t="n">
         <v>6</v>
       </c>
       <c r="BP5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BQ5" t="n">
         <v>6.6</v>
       </c>
       <c r="BR5" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BS5" t="n">
         <v>6.8</v>
@@ -1820,29 +1820,29 @@
         <v>4.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BV5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BY5" t="n">
         <v>6.4</v>
       </c>
       <c r="BZ5" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>
@@ -1873,178 +1873,178 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>270</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>70</v>
+        <v>19.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
         <v>450</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="n">
-        <v>320</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
         <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="AS6" t="n">
         <v>9</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF6" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BG6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,40 +2053,40 @@
         <v>11</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>10</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>2.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I7" t="n">
         <v>3.85</v>
@@ -2169,10 +2169,10 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
@@ -2181,7 +2181,7 @@
         <v>1.71</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
         <v>13.5</v>
@@ -2205,7 +2205,7 @@
         <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -2220,7 +2220,7 @@
         <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
@@ -2235,7 +2235,7 @@
         <v>60</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>11.5</v>
@@ -2244,13 +2244,13 @@
         <v>22</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="AT7" t="n">
         <v>8.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>12.5</v>
@@ -2262,16 +2262,16 @@
         <v>13.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA7" t="n">
         <v>44</v>
       </c>
       <c r="BB7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC7" t="n">
         <v>22</v>
@@ -2280,7 +2280,7 @@
         <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
         <v>18.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.51</v>
@@ -2408,55 +2408,55 @@
         <v>2.98</v>
       </c>
       <c r="O8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
         <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
         <v>100</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF8" t="n">
         <v>14</v>
@@ -2465,16 +2465,16 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
         <v>30</v>
       </c>
       <c r="AK8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
@@ -2483,10 +2483,10 @@
         <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AO8" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AP8" t="n">
         <v>9</v>
@@ -2495,13 +2495,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.8</v>
+        <v>26</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
@@ -2510,91 +2510,91 @@
         <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.8</v>
+        <v>38</v>
       </c>
       <c r="BB8" t="n">
-        <v>19</v>
+        <v>5.7</v>
       </c>
       <c r="BC8" t="n">
         <v>19</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.6</v>
+        <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
         <v>18.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.8</v>
+        <v>22</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BQ8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
         <v>5.9</v>
       </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BT8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BU8" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>2.1</v>
@@ -2644,43 +2644,43 @@
         <v>4.7</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
         <v>3.35</v>
       </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M9" t="n">
         <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P9" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="V9" t="n">
         <v>1.23</v>
@@ -2692,7 +2692,7 @@
         <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
         <v>36</v>
@@ -2710,7 +2710,7 @@
         <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
@@ -2719,43 +2719,43 @@
         <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
         <v>110</v>
       </c>
       <c r="AJ9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL9" t="n">
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
         <v>130</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
         <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
         <v>6.2</v>
@@ -2764,19 +2764,19 @@
         <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
         <v>19.5</v>
@@ -2785,70 +2785,70 @@
         <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BG9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK9" t="n">
         <v>8.4</v>
       </c>
-      <c r="BH9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO9" t="n">
         <v>3.7</v>
       </c>
       <c r="BP9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT9" t="n">
         <v>8</v>
       </c>
       <c r="BU9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV9" t="n">
         <v>46</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX9" t="n">
         <v>65</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -857,82 +857,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="K2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S2" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="X2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Y2" t="n">
-        <v>420</v>
+        <v>95</v>
       </c>
       <c r="Z2" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
         <v>19.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AE2" t="n">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="AF2" t="n">
         <v>10.5</v>
@@ -941,10 +941,10 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AI2" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AJ2" t="n">
         <v>8.800000000000001</v>
@@ -956,28 +956,28 @@
         <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AO2" t="n">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="AP2" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AQ2" t="n">
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU2" t="n">
         <v>15.5</v>
@@ -986,55 +986,55 @@
         <v>24</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
         <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BG2" t="n">
         <v>15</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BN2" t="n">
         <v>3.9</v>
@@ -1043,34 +1043,34 @@
         <v>3.55</v>
       </c>
       <c r="BP2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS2" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BT2" t="n">
         <v>19.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G3" t="n">
         <v>1.41</v>
@@ -1120,16 +1120,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K3" t="n">
         <v>5.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -1138,109 +1138,109 @@
         <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
         <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W3" t="n">
         <v>3.45</v>
       </c>
       <c r="X3" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="Y3" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="Z3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA3" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC3" t="n">
         <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AE3" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AF3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ3" t="n">
         <v>13</v>
       </c>
       <c r="AK3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL3" t="n">
         <v>28</v>
       </c>
       <c r="AM3" t="n">
-        <v>140</v>
+        <v>790</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AO3" t="n">
         <v>120</v>
       </c>
       <c r="AP3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
         <v>34</v>
       </c>
       <c r="AR3" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AT3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU3" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>10.5</v>
       </c>
       <c r="AV3" t="n">
         <v>27</v>
       </c>
       <c r="AW3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX3" t="n">
         <v>9.199999999999999</v>
@@ -1249,10 +1249,10 @@
         <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB3" t="n">
         <v>11.5</v>
@@ -1261,19 +1261,19 @@
         <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="BF3" t="n">
         <v>4.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BI3" t="n">
         <v>3.85</v>
@@ -1288,43 +1288,43 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BQ3" t="n">
         <v>5.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS3" t="n">
         <v>14</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>
@@ -1365,46 +1365,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="I4" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="J4" t="n">
         <v>2.76</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S4" t="n">
         <v>1.02</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.54</v>
       </c>
       <c r="T4" t="n">
         <v>1.83</v>
@@ -1413,7 +1413,7 @@
         <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="W4" t="n">
         <v>1.23</v>
@@ -1485,7 +1485,7 @@
         <v>1.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AU4" t="n">
         <v>5.1</v>
@@ -1494,31 +1494,31 @@
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AY4" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="BA4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BB4" t="n">
         <v>1.92</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BC4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.93</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.94</v>
       </c>
       <c r="BF4" t="n">
         <v>1.93</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>
@@ -1619,70 +1619,70 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="H5" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="I5" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="O5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="Z5" t="n">
         <v>13.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB5" t="n">
         <v>12</v>
@@ -1691,28 +1691,28 @@
         <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG5" t="n">
         <v>20</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI5" t="n">
         <v>70</v>
       </c>
       <c r="AJ5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK5" t="n">
         <v>130</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>90</v>
       </c>
       <c r="AL5" t="n">
         <v>120</v>
@@ -1727,34 +1727,34 @@
         <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW5" t="n">
         <v>23</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>25</v>
       </c>
       <c r="AX5" t="n">
         <v>24</v>
       </c>
       <c r="AY5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ5" t="n">
         <v>21</v>
@@ -1763,86 +1763,86 @@
         <v>48</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BC5" t="n">
         <v>32</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="BJ5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN5" t="n">
         <v>8.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT5" t="n">
         <v>4.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BX5" t="n">
         <v>44</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
         <v>2.12</v>
@@ -1915,109 +1915,109 @@
         <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="X6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z6" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
         <v>450</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AO6" t="n">
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BB6" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BC6" t="n">
         <v>18</v>
@@ -2026,19 +2026,19 @@
         <v>27</v>
       </c>
       <c r="BE6" t="n">
-        <v>28</v>
+        <v>9.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="n">
         <v>3.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
@@ -2050,43 +2050,43 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>11</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>10</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>
@@ -2136,10 +2136,10 @@
         <v>3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
         <v>3.3</v>
@@ -2151,7 +2151,7 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O7" t="n">
         <v>1.38</v>
@@ -2163,16 +2163,16 @@
         <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
@@ -2187,7 +2187,7 @@
         <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
         <v>90</v>
@@ -2205,7 +2205,7 @@
         <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -2247,19 +2247,19 @@
         <v>48</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU7" t="n">
         <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
         <v>32</v>
       </c>
       <c r="AX7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
@@ -2289,68 +2289,68 @@
         <v>38</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BJ7" t="n">
         <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
         <v>18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR7" t="n">
         <v>34</v>
       </c>
       <c r="BS7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV7" t="n">
         <v>29</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BZ7" t="n">
         <v>32</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>
@@ -2381,94 +2381,94 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H8" t="n">
         <v>3.9</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="O8" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T8" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V8" t="n">
         <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AB8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC8" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
         <v>30</v>
@@ -2477,31 +2477,31 @@
         <v>30</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AN8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AP8" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
@@ -2510,40 +2510,40 @@
         <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.9</v>
+        <v>38</v>
       </c>
       <c r="AX8" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.7</v>
+        <v>22</v>
       </c>
       <c r="BC8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD8" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="BE8" t="n">
         <v>6.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG8" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BI8" t="n">
         <v>2.48</v>
@@ -2552,16 +2552,16 @@
         <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BO8" t="n">
         <v>3.8</v>
@@ -2570,31 +2570,31 @@
         <v>19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BT8" t="n">
         <v>8</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>
@@ -2635,43 +2635,43 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M9" t="n">
         <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -2683,19 +2683,19 @@
         <v>1.78</v>
       </c>
       <c r="V9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA9" t="n">
         <v>140</v>
@@ -2713,7 +2713,7 @@
         <v>95</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
@@ -2725,25 +2725,25 @@
         <v>110</v>
       </c>
       <c r="AJ9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK9" t="n">
         <v>29</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
         <v>220</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AO9" t="n">
         <v>130</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
         <v>10.5</v>
@@ -2752,7 +2752,7 @@
         <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AT9" t="n">
         <v>6</v>
@@ -2761,10 +2761,10 @@
         <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
@@ -2776,43 +2776,43 @@
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BD9" t="n">
         <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ9" t="n">
         <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
         <v>4.8</v>
@@ -2824,16 +2824,16 @@
         <v>18</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU9" t="n">
         <v>6.2</v>
@@ -2842,13 +2842,13 @@
         <v>46</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -863,19 +863,19 @@
         <v>1.19</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
@@ -887,61 +887,61 @@
         <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R2" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
         <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="X2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y2" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="Z2" t="n">
-        <v>240</v>
+        <v>320</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AD2" t="n">
         <v>80</v>
       </c>
       <c r="AE2" t="n">
-        <v>370</v>
+        <v>570</v>
       </c>
       <c r="AF2" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AI2" t="n">
         <v>240</v>
@@ -950,127 +950,127 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AO2" t="n">
-        <v>460</v>
+        <v>580</v>
       </c>
       <c r="AP2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AQ2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AR2" t="n">
-        <v>15</v>
+        <v>190</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
         <v>11.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AW2" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AX2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.5</v>
+        <v>150</v>
       </c>
       <c r="BB2" t="n">
         <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>14.5</v>
+        <v>120</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BG2" t="n">
+        <v>230</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>15</v>
       </c>
-      <c r="BH2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BK2" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM2" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BP2" t="n">
         <v>6</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BR2" t="n">
+        <v>910</v>
+      </c>
+      <c r="BS2" t="n">
         <v>20</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>13.5</v>
       </c>
       <c r="BT2" t="n">
         <v>19.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BW2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BY2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="H3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="K3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -1138,73 +1138,73 @@
         <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.26</v>
       </c>
-      <c r="T3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.08</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="X3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Y3" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="Z3" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AA3" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE3" t="n">
         <v>260</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>110</v>
       </c>
       <c r="AF3" t="n">
         <v>10.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="AJ3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL3" t="n">
         <v>28</v>
@@ -1213,73 +1213,73 @@
         <v>790</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AP3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ3" t="n">
         <v>34</v>
       </c>
       <c r="AR3" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU3" t="n">
         <v>11</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>11.5</v>
       </c>
       <c r="AV3" t="n">
         <v>27</v>
       </c>
       <c r="AW3" t="n">
-        <v>16.5</v>
+        <v>75</v>
       </c>
       <c r="AX3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>48</v>
+        <v>16.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BE3" t="n">
-        <v>48</v>
+        <v>15.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
         <v>8.4</v>
@@ -1288,43 +1288,43 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BP3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
         <v>14</v>
       </c>
       <c r="BT3" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -1368,43 +1368,43 @@
         <v>3.35</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="I4" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="J4" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1</v>
+        <v>2.92</v>
       </c>
       <c r="L4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="P4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="T4" t="n">
         <v>1.83</v>
@@ -1413,115 +1413,115 @@
         <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="AH4" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AJ4" t="n">
         <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AL4" t="n">
-        <v>540</v>
+        <v>170</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.9</v>
+        <v>16.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.92</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.86</v>
+        <v>21</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.82</v>
+        <v>17.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.84</v>
+        <v>25</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>22</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.92</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.89</v>
+        <v>28</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.92</v>
+        <v>22</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.93</v>
+        <v>46</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.93</v>
+        <v>5.5</v>
       </c>
       <c r="BG4" t="n">
         <v>9</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>1.97</v>
+        <v>2.52</v>
       </c>
       <c r="I5" t="n">
-        <v>2.24</v>
+        <v>2.68</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.68</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="P5" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="W5" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="X5" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5" t="n">
         <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AO5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS5" t="n">
         <v>34</v>
       </c>
-      <c r="AP5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>21</v>
-      </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>23</v>
       </c>
-      <c r="AX5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>21</v>
-      </c>
       <c r="BA5" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="BC5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BD5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BN5" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BV5" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BX5" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BY5" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BZ5" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -1873,34 +1873,34 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
         <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
         <v>1.81</v>
@@ -1912,10 +1912,10 @@
         <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U6" t="n">
         <v>1.87</v>
@@ -1924,10 +1924,10 @@
         <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
         <v>18</v>
@@ -1948,7 +1948,7 @@
         <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AF6" t="n">
         <v>10.5</v>
@@ -1960,7 +1960,7 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>450</v>
+        <v>260</v>
       </c>
       <c r="AJ6" t="n">
         <v>19</v>
@@ -1969,7 +1969,7 @@
         <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
@@ -1978,31 +1978,31 @@
         <v>14.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>290</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>14.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AX6" t="n">
         <v>8.800000000000001</v>
@@ -2011,13 +2011,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC6" t="n">
         <v>18</v>
@@ -2026,19 +2026,19 @@
         <v>27</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.6</v>
+        <v>55</v>
       </c>
       <c r="BF6" t="n">
         <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="BH6" t="n">
         <v>3.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
@@ -2062,10 +2062,10 @@
         <v>13</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS6" t="n">
         <v>9.199999999999999</v>
@@ -2074,19 +2074,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>2.32</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H7" t="n">
         <v>3.65</v>
@@ -2139,10 +2139,10 @@
         <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
         <v>1.46</v>
@@ -2151,64 +2151,64 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
         <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA7" t="n">
         <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
         <v>7.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
         <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
         <v>18</v>
@@ -2217,19 +2217,19 @@
         <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
         <v>60</v>
@@ -2250,10 +2250,10 @@
         <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW7" t="n">
         <v>32</v>
@@ -2265,28 +2265,28 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BB7" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BC7" t="n">
         <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.800000000000001</v>
+        <v>65</v>
       </c>
       <c r="BF7" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH7" t="n">
         <v>3.15</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -2381,88 +2381,88 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
         <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="X8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
@@ -2471,130 +2471,130 @@
         <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA8" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BG8" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BN8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BP8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H9" t="n">
         <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
         <v>1.58</v>
@@ -2659,10 +2659,10 @@
         <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P9" t="n">
         <v>1.58</v>
@@ -2674,10 +2674,10 @@
         <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
         <v>1.78</v>
@@ -2686,10 +2686,10 @@
         <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X9" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y9" t="n">
         <v>13</v>
@@ -2698,7 +2698,7 @@
         <v>34</v>
       </c>
       <c r="AA9" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AB9" t="n">
         <v>7.4</v>
@@ -2710,7 +2710,7 @@
         <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
         <v>12.5</v>
@@ -2722,10 +2722,10 @@
         <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK9" t="n">
         <v>29</v>
@@ -2737,10 +2737,10 @@
         <v>220</v>
       </c>
       <c r="AN9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AP9" t="n">
         <v>8</v>
@@ -2749,55 +2749,55 @@
         <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT9" t="n">
         <v>6</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
         <v>16.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="AX9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BC9" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
         <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI9" t="n">
         <v>2.36</v>
@@ -2806,13 +2806,13 @@
         <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
         <v>4.8</v>
@@ -2821,34 +2821,34 @@
         <v>3.7</v>
       </c>
       <c r="BP9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>6.8</v>
       </c>
       <c r="BR9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT9" t="n">
         <v>7.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV9" t="n">
         <v>46</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,234 +843,234 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>8.800000000000001</v>
+        <v>110</v>
       </c>
       <c r="K2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>6.2</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1.16</v>
       </c>
       <c r="T2" t="n">
-        <v>2.14</v>
+        <v>2.54</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="X2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM2" t="n">
         <v>320</v>
       </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>570</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>240</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>190</v>
-      </c>
       <c r="AN2" t="n">
-        <v>3.05</v>
+        <v>1.33</v>
       </c>
       <c r="AO2" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="AR2" t="n">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>250</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.5</v>
+        <v>250</v>
       </c>
       <c r="AU2" t="n">
-        <v>17.5</v>
+        <v>250</v>
       </c>
       <c r="AV2" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AW2" t="n">
-        <v>23</v>
+        <v>250</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>250</v>
       </c>
       <c r="AY2" t="n">
-        <v>11.5</v>
+        <v>250</v>
       </c>
       <c r="AZ2" t="n">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="BA2" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.78</v>
+        <v>1.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,244 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>CSD Central Ballester</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>CA Atlas</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.42</v>
+        <v>3.35</v>
       </c>
       <c r="G3" t="n">
-        <v>1.44</v>
+        <v>3.65</v>
       </c>
       <c r="H3" t="n">
-        <v>8.4</v>
+        <v>2.58</v>
       </c>
       <c r="I3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.76</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2</v>
+        <v>2.84</v>
       </c>
       <c r="K3" t="n">
-        <v>5.7</v>
+        <v>2.94</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="N3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S3" t="n">
         <v>6.4</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.32</v>
-      </c>
       <c r="T3" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2</v>
+        <v>1.37</v>
       </c>
       <c r="X3" t="n">
-        <v>44</v>
+        <v>7.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="AA3" t="n">
-        <v>270</v>
+        <v>65</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="AC3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV3" t="n">
         <v>12</v>
       </c>
-      <c r="AD3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF3" t="n">
+      <c r="AW3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL3" t="n">
+      <c r="AY3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB3" t="n">
         <v>28</v>
       </c>
-      <c r="AM3" t="n">
-        <v>790</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB3" t="n">
+      <c r="BC3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD3" t="n">
         <v>12</v>
       </c>
-      <c r="BC3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>16</v>
-      </c>
       <c r="BE3" t="n">
-        <v>15.5</v>
+        <v>100</v>
       </c>
       <c r="BF3" t="n">
         <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>
@@ -1356,246 +1356,246 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CSD Central Ballester</t>
+          <t>CA Claypole</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CA Atlas</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3.35</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H4" t="n">
         <v>2.48</v>
       </c>
       <c r="I4" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="J4" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
         <v>1.15</v>
       </c>
       <c r="N4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.2</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.83</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AB4" t="n">
         <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="n">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="AG4" t="n">
-        <v>95</v>
+        <v>17.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AI4" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AK4" t="n">
         <v>100</v>
       </c>
       <c r="AL4" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>95</v>
       </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>48</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF4" t="n">
         <v>12</v>
       </c>
-      <c r="AW4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CA Claypole</t>
+          <t>SER Caxias do Sul</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Canuelas</t>
+          <t>Anapolis GO</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>1.76</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="H5" t="n">
-        <v>2.52</v>
+        <v>5.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2.68</v>
+        <v>6.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="R5" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W5" t="n">
         <v>2.2</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X5" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>8</v>
+        <v>17.5</v>
       </c>
       <c r="Z5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC5" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>46</v>
-      </c>
       <c r="BD5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE5" t="n">
         <v>28</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BG5" t="n">
-        <v>40</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="BJ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP5" t="n">
         <v>13.5</v>
       </c>
-      <c r="BK5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>44</v>
-      </c>
       <c r="BQ5" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BU5" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,225 +1859,225 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anapolis GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.76</v>
+        <v>2.36</v>
       </c>
       <c r="G6" t="n">
-        <v>1.84</v>
+        <v>2.42</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.37</v>
       </c>
-      <c r="P6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W6" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH6" t="n">
         <v>18</v>
       </c>
-      <c r="Z6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AI6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN6" t="n">
         <v>24</v>
       </c>
-      <c r="AE6" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AO6" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AP6" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.6</v>
+        <v>48</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
         <v>50</v>
       </c>
       <c r="BB6" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BC6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP6" t="n">
         <v>18</v>
       </c>
-      <c r="BD6" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>60</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>13</v>
-      </c>
       <c r="BQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV6" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="BW6" t="n">
         <v>10.5</v>
@@ -2086,24 +2086,24 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,244 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="H7" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.31</v>
       </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.36</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="X7" t="n">
         <v>12</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AP7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>42</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>10</v>
-      </c>
       <c r="BK7" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="BN7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="BP7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="BT7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
         <v>7</v>
       </c>
-      <c r="BU7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>29</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>
@@ -2372,118 +2372,118 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Amazonas FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="O8" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="P8" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="R8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.25</v>
       </c>
-      <c r="S8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.31</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
         <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN8" t="n">
         <v>28</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>32</v>
       </c>
       <c r="AO8" t="n">
         <v>160</v>
@@ -2492,109 +2492,109 @@
         <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>60</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>46</v>
-      </c>
       <c r="BH8" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BO8" t="n">
         <v>3.7</v>
       </c>
       <c r="BP8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BR8" t="n">
         <v>42</v>
       </c>
       <c r="BS8" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BU8" t="n">
         <v>6</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY8" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,261 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 12:11:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Volta Redonda</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Amazonas FC</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>70</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-30 12:11:53</t>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>CSD Central Ballester</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>CA Atlas</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>1.01</v>
+        <v>710</v>
       </c>
       <c r="H2" t="n">
-        <v>320</v>
+        <v>1.28</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>110</v>
+        <v>5.2</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -881,43 +881,43 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R2" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="S2" t="n">
-        <v>1.16</v>
+        <v>25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="W2" t="n">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -926,10 +926,10 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
@@ -938,85 +938,85 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>790</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.33</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>250</v>
+        <v>2.32</v>
       </c>
       <c r="AR2" t="n">
-        <v>250</v>
+        <v>4.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>250</v>
+        <v>16.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>250</v>
+        <v>5.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>250</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="AX2" t="n">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>250</v>
+        <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>250</v>
+        <v>44</v>
       </c>
       <c r="BA2" t="n">
-        <v>250</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BD2" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BE2" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>140</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
@@ -1102,246 +1102,246 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CSD Central Ballester</t>
+          <t>CA Claypole</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CA Atlas</t>
+          <t>Canuelas</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="G3" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.58</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>2.76</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>2.84</v>
+        <v>1.8</v>
       </c>
       <c r="K3" t="n">
-        <v>2.94</v>
+        <v>1.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.15</v>
+        <v>1.78</v>
       </c>
       <c r="N3" t="n">
-        <v>2.26</v>
+        <v>1.23</v>
       </c>
       <c r="O3" t="n">
-        <v>1.67</v>
+        <v>4.9</v>
       </c>
       <c r="P3" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.05</v>
+        <v>22</v>
       </c>
       <c r="R3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S3" t="n">
+        <v>95</v>
+      </c>
+      <c r="T3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.12</v>
       </c>
-      <c r="S3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>7.8</v>
+        <v>2.28</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>5.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>27</v>
+        <v>6.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="AE3" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AG3" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>170</v>
       </c>
-      <c r="AM3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>25</v>
-      </c>
       <c r="BA3" t="n">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="BB3" t="n">
-        <v>28</v>
+        <v>230</v>
       </c>
       <c r="BC3" t="n">
-        <v>22</v>
+        <v>270</v>
       </c>
       <c r="BD3" t="n">
-        <v>12</v>
+        <v>420</v>
       </c>
       <c r="BE3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>15</v>
+        <v>380</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,171 +1351,171 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CA Claypole</t>
+          <t>SER Caxias do Sul</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Canuelas</t>
+          <t>Anapolis GO</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.35</v>
+        <v>1.72</v>
       </c>
       <c r="G4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.6</v>
       </c>
-      <c r="H4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.17</v>
       </c>
-      <c r="S4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.6</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.38</v>
+        <v>2.28</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB4" t="n">
         <v>7.4</v>
       </c>
-      <c r="Z4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN4" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH4" t="n">
+      <c r="AO4" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD4" t="n">
         <v>29</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>48</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>12.5</v>
       </c>
       <c r="BE4" t="n">
         <v>28</v>
@@ -1524,78 +1524,78 @@
         <v>12</v>
       </c>
       <c r="BG4" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.2</v>
+        <v>2.86</v>
       </c>
       <c r="BJ4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP4" t="n">
         <v>12.5</v>
       </c>
-      <c r="BK4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
+      <c r="BQ4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
         <v>10</v>
       </c>
-      <c r="BN4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>38</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>65</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BX4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anapolis GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
+        <v>3.65</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="X5" t="n">
         <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE5" t="n">
         <v>44</v>
       </c>
-      <c r="AA5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AF5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG5" t="n">
+      <c r="BR5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS5" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP5" t="n">
+      <c r="BT5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW5" t="n">
         <v>10</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ5" t="n">
+      <c r="BX5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY5" t="n">
         <v>11</v>
       </c>
-      <c r="BK5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,141 +1859,141 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>2.14</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="I6" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="T6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.85</v>
       </c>
-      <c r="U6" t="n">
-        <v>2.12</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="X6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL6" t="n">
         <v>55</v>
       </c>
-      <c r="AF6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>44</v>
-      </c>
       <c r="AM6" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AN6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS6" t="n">
         <v>60</v>
       </c>
-      <c r="AP6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>48</v>
-      </c>
       <c r="AT6" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
         <v>6.6</v>
@@ -2002,101 +2002,101 @@
         <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX6" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB6" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BD6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR6" t="n">
         <v>38</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BS6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX6" t="n">
         <v>65</v>
       </c>
-      <c r="BF6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>42</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT6" t="n">
+      <c r="BY6" t="n">
         <v>7</v>
       </c>
-      <c r="BU6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>12</v>
-      </c>
       <c r="BZ6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
@@ -2118,49 +2118,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Amazonas FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H7" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
@@ -2169,178 +2169,178 @@
         <v>4.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
         <v>85</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>100</v>
       </c>
       <c r="AJ7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AP7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AS7" t="n">
-        <v>70</v>
+        <v>8.4</v>
       </c>
       <c r="AT7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU7" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV7" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
         <v>21</v>
       </c>
       <c r="BC7" t="n">
-        <v>19.5</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN7" t="n">
         <v>4.8</v>
       </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BO7" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BP7" t="n">
         <v>17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU7" t="n">
         <v>6</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,261 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Volta Redonda</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Amazonas FC</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>70</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-30.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I2" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>2.58</v>
       </c>
       <c r="K2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="S2" t="n">
+        <v>30</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>520</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>530</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT2" t="n">
         <v>3.8</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AU2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>75</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC2" t="n">
         <v>55</v>
       </c>
-      <c r="AA2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>18</v>
-      </c>
       <c r="BD2" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="BE2" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>13.5</v>
+        <v>60</v>
       </c>
       <c r="BG2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>2.44</v>
+        <v>6.2</v>
       </c>
       <c r="H3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J3" t="n">
         <v>3.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>3.55</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>2.22</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7</v>
+        <v>1.19</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>5.7</v>
       </c>
       <c r="Z3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS3" t="n">
         <v>24</v>
       </c>
-      <c r="AA3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>75</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>9.4</v>
       </c>
-      <c r="AC3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BK3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.7</v>
+        <v>23</v>
       </c>
       <c r="BP3" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BR3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.8</v>
+        <v>1.31</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>1.27</v>
       </c>
       <c r="BV3" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BW3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>800</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>32</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>830</v>
+      </c>
+      <c r="CA3" t="n">
         <v>20</v>
       </c>
-      <c r="BX3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>32</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -1365,220 +1365,220 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O4" t="n">
         <v>1.51</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.45</v>
-      </c>
       <c r="P4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.69</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="V4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.28</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y4" t="n">
         <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AB4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC4" t="n">
         <v>8.4</v>
       </c>
-      <c r="AC4" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AI4" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN4" t="n">
         <v>25</v>
       </c>
-      <c r="AL4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>21</v>
-      </c>
       <c r="AO4" t="n">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
         <v>27</v>
       </c>
       <c r="AS4" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BB4" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BC4" t="n">
         <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BE4" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="BF4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BP4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BV4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY4" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -1619,220 +1619,220 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="X5" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF5" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG5" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AJ5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AM5" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AN5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO5" t="n">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>110</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>170</v>
+      </c>
+      <c r="BF5" t="n">
         <v>18.5</v>
       </c>
-      <c r="BA5" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>90</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>19</v>
-      </c>
       <c r="BG5" t="n">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.94</v>
+        <v>2.64</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM5" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BP5" t="n">
         <v>17</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BR5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>75</v>
+      </c>
+      <c r="BW5" t="n">
         <v>38</v>
       </c>
-      <c r="BS5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY5" t="n">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
